--- a/data/excel_sql/3.-tables_db.xlsx
+++ b/data/excel_sql/3.-tables_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\excel_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E969DA8-4BD8-485C-9B2D-5C09C3A6D3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9414EB4-0960-423C-BB1B-350980C4F9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="1304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="1438">
   <si>
     <t>Aborto</t>
   </si>
@@ -3952,6 +3952,408 @@
   </si>
   <si>
     <t>[2013, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024]</t>
+  </si>
+  <si>
+    <t>2.1.</t>
+  </si>
+  <si>
+    <t>10.8.</t>
+  </si>
+  <si>
+    <t>2.2.</t>
+  </si>
+  <si>
+    <t>3.1.1.</t>
+  </si>
+  <si>
+    <t>3.1.2.</t>
+  </si>
+  <si>
+    <t>3.1.3.</t>
+  </si>
+  <si>
+    <t>3.2.</t>
+  </si>
+  <si>
+    <t>4.4.1.</t>
+  </si>
+  <si>
+    <t>3.3.1.</t>
+  </si>
+  <si>
+    <t>3.3.2.</t>
+  </si>
+  <si>
+    <t>3.3.3.</t>
+  </si>
+  <si>
+    <t>3.4.1.</t>
+  </si>
+  <si>
+    <t>3.4.2.</t>
+  </si>
+  <si>
+    <t>3.5.1.</t>
+  </si>
+  <si>
+    <t>3.5.2.</t>
+  </si>
+  <si>
+    <t>3.5.3.</t>
+  </si>
+  <si>
+    <t>4.2.1.1.</t>
+  </si>
+  <si>
+    <t>4.2.1.2.</t>
+  </si>
+  <si>
+    <t>4.2.1.3.</t>
+  </si>
+  <si>
+    <t>4.2.1.4.</t>
+  </si>
+  <si>
+    <t>4.2.2.1.</t>
+  </si>
+  <si>
+    <t>4.2.2.2.</t>
+  </si>
+  <si>
+    <t>4.2.2.3.</t>
+  </si>
+  <si>
+    <t>4.2.2.4.</t>
+  </si>
+  <si>
+    <t>4.2.2.5.</t>
+  </si>
+  <si>
+    <t>4.2.2.6.</t>
+  </si>
+  <si>
+    <t>4.2.2.7.</t>
+  </si>
+  <si>
+    <t>4.2.2.8.</t>
+  </si>
+  <si>
+    <t>4.2.2.9.</t>
+  </si>
+  <si>
+    <t>4.2.2.10.</t>
+  </si>
+  <si>
+    <t>4.3.1.1.</t>
+  </si>
+  <si>
+    <t>4.3.1.2.</t>
+  </si>
+  <si>
+    <t>4.3.1.3.</t>
+  </si>
+  <si>
+    <t>4.3.1.4.</t>
+  </si>
+  <si>
+    <t>4.3.1.5.</t>
+  </si>
+  <si>
+    <t>4.4.1.1.</t>
+  </si>
+  <si>
+    <t>4.4.1.2.</t>
+  </si>
+  <si>
+    <t>4.4.1.3.</t>
+  </si>
+  <si>
+    <t>4.4.1.4.</t>
+  </si>
+  <si>
+    <t>4.4.1.5.</t>
+  </si>
+  <si>
+    <t>4.4.1.6.</t>
+  </si>
+  <si>
+    <t>4.4.1.7.</t>
+  </si>
+  <si>
+    <t>4.5.1.1.</t>
+  </si>
+  <si>
+    <t>4.5.1.2.</t>
+  </si>
+  <si>
+    <t>4.6.1.</t>
+  </si>
+  <si>
+    <t>4.6.2.1.</t>
+  </si>
+  <si>
+    <t>4.6.2.2.</t>
+  </si>
+  <si>
+    <t>4.7.1.1.</t>
+  </si>
+  <si>
+    <t>4.7.2.2.</t>
+  </si>
+  <si>
+    <t>4.7.1.2.</t>
+  </si>
+  <si>
+    <t>4.7.1.3.</t>
+  </si>
+  <si>
+    <t>4.7.1.4.</t>
+  </si>
+  <si>
+    <t>4.7.2.1.</t>
+  </si>
+  <si>
+    <t>4.7.2.3.</t>
+  </si>
+  <si>
+    <t>4.8.1.</t>
+  </si>
+  <si>
+    <t>4.8.2.1.</t>
+  </si>
+  <si>
+    <t>4.8.2.2.</t>
+  </si>
+  <si>
+    <t>4.9.1.1.</t>
+  </si>
+  <si>
+    <t>4.9.1.2.</t>
+  </si>
+  <si>
+    <t>4.9.2.1.</t>
+  </si>
+  <si>
+    <t>4.9.2.2.</t>
+  </si>
+  <si>
+    <t>4.9.2.3.</t>
+  </si>
+  <si>
+    <t>4.10.1.1.</t>
+  </si>
+  <si>
+    <t>4.10.1.2.</t>
+  </si>
+  <si>
+    <t>4.10.1.3.</t>
+  </si>
+  <si>
+    <t>4.10.1.4.</t>
+  </si>
+  <si>
+    <t>4.10.1.5.</t>
+  </si>
+  <si>
+    <t>4.10.1.6.</t>
+  </si>
+  <si>
+    <t>4.10.1.7.</t>
+  </si>
+  <si>
+    <t>4.10.1.8.</t>
+  </si>
+  <si>
+    <t>4.11.1.1.</t>
+  </si>
+  <si>
+    <t>4.11.1.2.</t>
+  </si>
+  <si>
+    <t>4.12.1.1.</t>
+  </si>
+  <si>
+    <t>4.13.1.1.</t>
+  </si>
+  <si>
+    <t>4.12.1.2.</t>
+  </si>
+  <si>
+    <t>4.15.1.1.</t>
+  </si>
+  <si>
+    <t>4.13.1.2.</t>
+  </si>
+  <si>
+    <t>4.13.2.1.</t>
+  </si>
+  <si>
+    <t>4.13.2.2.</t>
+  </si>
+  <si>
+    <t>4.13.2.3.</t>
+  </si>
+  <si>
+    <t>4.13.2.4.</t>
+  </si>
+  <si>
+    <t>4.13.2.5.</t>
+  </si>
+  <si>
+    <t>4.13.2.6.</t>
+  </si>
+  <si>
+    <t>4.13.2.7.</t>
+  </si>
+  <si>
+    <t>4.13.2.8.</t>
+  </si>
+  <si>
+    <t>4.13.2.9.</t>
+  </si>
+  <si>
+    <t>4.13.2.10.</t>
+  </si>
+  <si>
+    <t>4.13.2.11.</t>
+  </si>
+  <si>
+    <t>4.13.2.12.</t>
+  </si>
+  <si>
+    <t>4.13.2.13.</t>
+  </si>
+  <si>
+    <t>4.13.2.14.</t>
+  </si>
+  <si>
+    <t>4.13.2.15.</t>
+  </si>
+  <si>
+    <t>4.13.2.16.</t>
+  </si>
+  <si>
+    <t>4.13.2.17.</t>
+  </si>
+  <si>
+    <t>4.14.1.1.</t>
+  </si>
+  <si>
+    <t>4.14.1.2.</t>
+  </si>
+  <si>
+    <t>4.15.1.2.</t>
+  </si>
+  <si>
+    <t>4.15.1.3.</t>
+  </si>
+  <si>
+    <t>4.15.1.4.</t>
+  </si>
+  <si>
+    <t>4.15.1.5.</t>
+  </si>
+  <si>
+    <t>4.15.1.6.</t>
+  </si>
+  <si>
+    <t>4.15.1.7.</t>
+  </si>
+  <si>
+    <t>4.15.1.8.</t>
+  </si>
+  <si>
+    <t>4.15.1.9.</t>
+  </si>
+  <si>
+    <t>4.15.1.10.</t>
+  </si>
+  <si>
+    <t>4.15.1.11.</t>
+  </si>
+  <si>
+    <t>4.15.1.12.</t>
+  </si>
+  <si>
+    <t>4.15.1.13.</t>
+  </si>
+  <si>
+    <t>4.15.1.14.</t>
+  </si>
+  <si>
+    <t>4.15.1.15.</t>
+  </si>
+  <si>
+    <t>4.15.1.16.</t>
+  </si>
+  <si>
+    <t>4.15.1.17.</t>
+  </si>
+  <si>
+    <t>4.15.1.18.</t>
+  </si>
+  <si>
+    <t>4.15.1.19.</t>
+  </si>
+  <si>
+    <t>4.15.1.20.</t>
+  </si>
+  <si>
+    <t>4.15.1.21.</t>
+  </si>
+  <si>
+    <t>4.15.1.22.</t>
+  </si>
+  <si>
+    <t>4.15.1.23.</t>
+  </si>
+  <si>
+    <t>4.15.1.24.</t>
+  </si>
+  <si>
+    <t>4.15.1.25.</t>
+  </si>
+  <si>
+    <t>4.15.1.26.</t>
+  </si>
+  <si>
+    <t>10.1.</t>
+  </si>
+  <si>
+    <t>10.2.</t>
+  </si>
+  <si>
+    <t>10.3.</t>
+  </si>
+  <si>
+    <t>10.4.</t>
+  </si>
+  <si>
+    <t>10.5.</t>
+  </si>
+  <si>
+    <t>10.6.</t>
+  </si>
+  <si>
+    <t>10.7.</t>
+  </si>
+  <si>
+    <t>10.9.</t>
+  </si>
+  <si>
+    <t>10.10.</t>
+  </si>
+  <si>
+    <t>10.11.</t>
+  </si>
+  <si>
+    <t>10.12.</t>
+  </si>
+  <si>
+    <t>10.13.</t>
+  </si>
+  <si>
+    <t>10.14.</t>
   </si>
 </sst>
 </file>
@@ -4013,7 +4415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4030,38 +4432,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -4102,6 +4478,33 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4166,32 +4569,32 @@
     <tableColumn id="10" xr3:uid="{010B5077-EADB-4D64-B9D2-B1BE619927D4}" name="level"/>
     <tableColumn id="3" xr3:uid="{81FB6481-665F-4EC2-B18A-967202B37711}" name="name"/>
     <tableColumn id="4" xr3:uid="{5C408E3F-7EA0-4A74-9045-F0386B32748F}" name="status"/>
-    <tableColumn id="8" xr3:uid="{13CC9401-93CE-4134-BBE7-7E87C69DE5BA}" name="num_fechas" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{13CC9401-93CE-4134-BBE7-7E87C69DE5BA}" name="num_fechas" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{6415267F-4AFB-4E4A-95AD-51A014CB2BD0}" name="rango_fechas"/>
-    <tableColumn id="5" xr3:uid="{1F40335B-FDB9-4DB2-8D9C-5270D6F3B67A}" name="value" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{813CBB08-1D3D-43A8-8DEA-157F6DDF6F5F}" name="rows_in" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{FE5A63A0-C348-4543-ABB3-F94D2481FABA}" name="rows_out" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{1C7B014A-CE1E-4453-A91D-203FC4529D4A}" name="Obs" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{F5E83BC7-4C67-41B4-86A6-F9A4F64E2DC9}" name="Columna1" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{8CC6085E-5649-4894-BFD6-A0767D895C56}" name="Columna2" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{2C4EDC8C-3D0B-4A79-BB23-4CEC4D7E1AE8}" name="Columna3" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{7563D4A7-FE1D-4A5A-8868-52C79D499D5D}" name="Columna4" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{1F40335B-FDB9-4DB2-8D9C-5270D6F3B67A}" name="value" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{813CBB08-1D3D-43A8-8DEA-157F6DDF6F5F}" name="rows_in" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{FE5A63A0-C348-4543-ABB3-F94D2481FABA}" name="rows_out" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{1C7B014A-CE1E-4453-A91D-203FC4529D4A}" name="Obs" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{F5E83BC7-4C67-41B4-86A6-F9A4F64E2DC9}" name="Columna1" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{8CC6085E-5649-4894-BFD6-A0767D895C56}" name="Columna2" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{2C4EDC8C-3D0B-4A79-BB23-4CEC4D7E1AE8}" name="Columna3" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{7563D4A7-FE1D-4A5A-8868-52C79D499D5D}" name="Columna4" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}" name="Tabla2" displayName="Tabla2" ref="B1:E421" totalsRowShown="0" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}" name="Tabla2" displayName="Tabla2" ref="B1:E421" totalsRowShown="0" dataDxfId="4">
   <autoFilter ref="B1:E421" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E421">
     <sortCondition ref="C1:C421"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8AF95AAF-7C97-4030-8813-E5F15884669B}" name="Estados" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{B4C15FDA-B2EC-4A1D-A81E-4B2725E564AF}" name="Centros" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{17CD0285-B341-43C7-8ACD-65A35D973F9E}" name="ID" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{A0FEF947-428C-44F8-B2A5-5E3ECB03347F}" name="LARGO" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{8AF95AAF-7C97-4030-8813-E5F15884669B}" name="Estados" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B4C15FDA-B2EC-4A1D-A81E-4B2725E564AF}" name="Centros" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{17CD0285-B341-43C7-8ACD-65A35D973F9E}" name="ID" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A0FEF947-428C-44F8-B2A5-5E3ECB03347F}" name="LARGO" dataDxfId="0">
       <calculatedColumnFormula>LEN(Tabla2[[#This Row],[Centros]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5603,7 +6006,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="8">
         <v>1</v>
       </c>
       <c r="C2" t="s">
@@ -5635,7 +6038,9 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="8" t="s">
+        <v>1304</v>
+      </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
@@ -5665,7 +6070,9 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="8" t="s">
+        <v>1306</v>
+      </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
@@ -5695,7 +6102,9 @@
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="8" t="s">
+        <v>1307</v>
+      </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
@@ -5725,6 +6134,9 @@
       <c r="A6">
         <v>6</v>
       </c>
+      <c r="B6" s="8" t="s">
+        <v>1308</v>
+      </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
@@ -5753,6 +6165,9 @@
       <c r="A7">
         <v>7</v>
       </c>
+      <c r="B7" s="8" t="s">
+        <v>1309</v>
+      </c>
       <c r="C7" t="s">
         <v>555</v>
       </c>
@@ -5781,6 +6196,9 @@
       <c r="A8">
         <v>8</v>
       </c>
+      <c r="B8" s="8" t="s">
+        <v>1310</v>
+      </c>
       <c r="C8" t="s">
         <v>556</v>
       </c>
@@ -5809,6 +6227,9 @@
       <c r="A9">
         <v>10</v>
       </c>
+      <c r="B9" s="8" t="s">
+        <v>1311</v>
+      </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -5836,6 +6257,9 @@
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>12</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1427</v>
       </c>
       <c r="C10" t="s">
         <v>716</v>
@@ -5855,6 +6279,9 @@
       <c r="A11">
         <v>13</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>1425</v>
+      </c>
       <c r="C11" t="s">
         <v>714</v>
       </c>
@@ -5883,6 +6310,9 @@
       <c r="A12">
         <v>14</v>
       </c>
+      <c r="B12" s="8" t="s">
+        <v>1426</v>
+      </c>
       <c r="C12" t="s">
         <v>715</v>
       </c>
@@ -5911,6 +6341,9 @@
       <c r="A13">
         <v>15</v>
       </c>
+      <c r="B13" s="8" t="s">
+        <v>1312</v>
+      </c>
       <c r="C13" t="s">
         <v>557</v>
       </c>
@@ -5939,6 +6372,9 @@
       <c r="A14">
         <v>16</v>
       </c>
+      <c r="B14" s="8" t="s">
+        <v>1313</v>
+      </c>
       <c r="C14" t="s">
         <v>558</v>
       </c>
@@ -5966,6 +6402,9 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>17</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1314</v>
       </c>
       <c r="C15" t="s">
         <v>559</v>
@@ -5985,6 +6424,9 @@
       <c r="A16">
         <v>19</v>
       </c>
+      <c r="B16" s="8" t="s">
+        <v>1315</v>
+      </c>
       <c r="C16" t="s">
         <v>560</v>
       </c>
@@ -6013,6 +6455,9 @@
       <c r="A17">
         <v>20</v>
       </c>
+      <c r="B17" s="8" t="s">
+        <v>1316</v>
+      </c>
       <c r="C17" t="s">
         <v>561</v>
       </c>
@@ -6041,6 +6486,9 @@
       <c r="A18">
         <v>22</v>
       </c>
+      <c r="B18" s="8" t="s">
+        <v>1317</v>
+      </c>
       <c r="C18" t="s">
         <v>562</v>
       </c>
@@ -6069,6 +6517,9 @@
       <c r="A19">
         <v>23</v>
       </c>
+      <c r="B19" s="8" t="s">
+        <v>1318</v>
+      </c>
       <c r="C19" t="s">
         <v>563</v>
       </c>
@@ -6097,6 +6548,9 @@
       <c r="A20">
         <v>24</v>
       </c>
+      <c r="B20" s="8" t="s">
+        <v>1319</v>
+      </c>
       <c r="C20" t="s">
         <v>564</v>
       </c>
@@ -6125,6 +6579,9 @@
       <c r="A21">
         <v>27</v>
       </c>
+      <c r="B21" s="8" t="s">
+        <v>1320</v>
+      </c>
       <c r="C21" t="s">
         <v>24</v>
       </c>
@@ -6153,6 +6610,9 @@
       <c r="A22">
         <v>28</v>
       </c>
+      <c r="B22" s="8" t="s">
+        <v>1321</v>
+      </c>
       <c r="C22" t="s">
         <v>16</v>
       </c>
@@ -6181,6 +6641,9 @@
       <c r="A23">
         <v>29</v>
       </c>
+      <c r="B23" s="8" t="s">
+        <v>1322</v>
+      </c>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -6209,6 +6672,9 @@
       <c r="A24">
         <v>30</v>
       </c>
+      <c r="B24" s="8" t="s">
+        <v>1323</v>
+      </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
@@ -6236,6 +6702,9 @@
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>31</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1428</v>
       </c>
       <c r="C25" t="s">
         <v>717</v>
@@ -6255,6 +6724,9 @@
       <c r="A26">
         <v>32</v>
       </c>
+      <c r="B26" s="8" t="s">
+        <v>1429</v>
+      </c>
       <c r="C26" t="s">
         <v>718</v>
       </c>
@@ -6283,6 +6755,9 @@
       <c r="A27">
         <v>33</v>
       </c>
+      <c r="B27" s="8" t="s">
+        <v>1430</v>
+      </c>
       <c r="C27" t="s">
         <v>719</v>
       </c>
@@ -6311,6 +6786,9 @@
       <c r="A28">
         <v>34</v>
       </c>
+      <c r="B28" s="8" t="s">
+        <v>1431</v>
+      </c>
       <c r="C28" t="s">
         <v>720</v>
       </c>
@@ -6338,6 +6816,9 @@
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>35</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>1305</v>
       </c>
       <c r="C29" t="s">
         <v>721</v>
@@ -6357,6 +6838,9 @@
       <c r="A30">
         <v>36</v>
       </c>
+      <c r="B30" s="8" t="s">
+        <v>1432</v>
+      </c>
       <c r="C30" t="s">
         <v>722</v>
       </c>
@@ -6384,6 +6868,9 @@
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>37</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1433</v>
       </c>
       <c r="C31" t="s">
         <v>723</v>
@@ -6403,6 +6890,9 @@
       <c r="A32">
         <v>38</v>
       </c>
+      <c r="B32" s="8" t="s">
+        <v>1434</v>
+      </c>
       <c r="C32" t="s">
         <v>724</v>
       </c>
@@ -6421,6 +6911,9 @@
       <c r="A33">
         <v>39</v>
       </c>
+      <c r="B33" s="8" t="s">
+        <v>1435</v>
+      </c>
       <c r="C33" t="s">
         <v>725</v>
       </c>
@@ -6439,6 +6932,9 @@
       <c r="A34">
         <v>40</v>
       </c>
+      <c r="B34" s="8" t="s">
+        <v>1436</v>
+      </c>
       <c r="C34" t="s">
         <v>726</v>
       </c>
@@ -6467,6 +6963,9 @@
       <c r="A35">
         <v>41</v>
       </c>
+      <c r="B35" s="8" t="s">
+        <v>1437</v>
+      </c>
       <c r="C35" t="s">
         <v>727</v>
       </c>
@@ -6495,6 +6994,9 @@
       <c r="A36">
         <v>43</v>
       </c>
+      <c r="B36" s="8" t="s">
+        <v>1324</v>
+      </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
@@ -6523,6 +7025,9 @@
       <c r="A37">
         <v>44</v>
       </c>
+      <c r="B37" s="8" t="s">
+        <v>1325</v>
+      </c>
       <c r="C37" t="s">
         <v>25</v>
       </c>
@@ -6551,6 +7056,9 @@
       <c r="A38">
         <v>46</v>
       </c>
+      <c r="B38" s="8" t="s">
+        <v>1326</v>
+      </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
@@ -6579,6 +7087,9 @@
       <c r="A39">
         <v>47</v>
       </c>
+      <c r="B39" s="8" t="s">
+        <v>1327</v>
+      </c>
       <c r="C39" t="s">
         <v>20</v>
       </c>
@@ -6607,6 +7118,9 @@
       <c r="A40">
         <v>48</v>
       </c>
+      <c r="B40" s="8" t="s">
+        <v>1328</v>
+      </c>
       <c r="C40" t="s">
         <v>11</v>
       </c>
@@ -6635,6 +7149,9 @@
       <c r="A41">
         <v>49</v>
       </c>
+      <c r="B41" s="8" t="s">
+        <v>1329</v>
+      </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
@@ -6663,6 +7180,9 @@
       <c r="A42">
         <v>50</v>
       </c>
+      <c r="B42" s="8" t="s">
+        <v>1330</v>
+      </c>
       <c r="C42" t="s">
         <v>8</v>
       </c>
@@ -6691,6 +7211,9 @@
       <c r="A43">
         <v>51</v>
       </c>
+      <c r="B43" s="8" t="s">
+        <v>1331</v>
+      </c>
       <c r="C43" t="s">
         <v>22</v>
       </c>
@@ -6719,6 +7242,9 @@
       <c r="A44">
         <v>52</v>
       </c>
+      <c r="B44" s="8" t="s">
+        <v>1332</v>
+      </c>
       <c r="C44" t="s">
         <v>26</v>
       </c>
@@ -6747,6 +7273,9 @@
       <c r="A45">
         <v>53</v>
       </c>
+      <c r="B45" s="8" t="s">
+        <v>1333</v>
+      </c>
       <c r="C45" t="s">
         <v>21</v>
       </c>
@@ -6775,6 +7304,9 @@
       <c r="A46">
         <v>56</v>
       </c>
+      <c r="B46" s="8" t="s">
+        <v>1334</v>
+      </c>
       <c r="C46" t="s">
         <v>566</v>
       </c>
@@ -6803,6 +7335,9 @@
       <c r="A47">
         <v>57</v>
       </c>
+      <c r="B47" s="8" t="s">
+        <v>1335</v>
+      </c>
       <c r="C47" t="s">
         <v>567</v>
       </c>
@@ -6830,6 +7365,9 @@
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>58</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1336</v>
       </c>
       <c r="C48" t="s">
         <v>568</v>
@@ -6849,6 +7387,9 @@
       <c r="A49">
         <v>59</v>
       </c>
+      <c r="B49" s="8" t="s">
+        <v>1337</v>
+      </c>
       <c r="C49" t="s">
         <v>569</v>
       </c>
@@ -6867,6 +7408,9 @@
       <c r="A50">
         <v>60</v>
       </c>
+      <c r="B50" s="8" t="s">
+        <v>1338</v>
+      </c>
       <c r="C50" t="s">
         <v>570</v>
       </c>
@@ -6895,6 +7439,9 @@
       <c r="A51">
         <v>63</v>
       </c>
+      <c r="B51" s="8" t="s">
+        <v>1339</v>
+      </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
@@ -6923,6 +7470,9 @@
       <c r="A52">
         <v>64</v>
       </c>
+      <c r="B52" s="8" t="s">
+        <v>1340</v>
+      </c>
       <c r="C52" t="s">
         <v>571</v>
       </c>
@@ -6951,6 +7501,9 @@
       <c r="A53">
         <v>65</v>
       </c>
+      <c r="B53" s="8" t="s">
+        <v>1341</v>
+      </c>
       <c r="C53" t="s">
         <v>572</v>
       </c>
@@ -6979,6 +7532,9 @@
       <c r="A54">
         <v>66</v>
       </c>
+      <c r="B54" s="8" t="s">
+        <v>1342</v>
+      </c>
       <c r="C54" t="s">
         <v>573</v>
       </c>
@@ -7007,6 +7563,9 @@
       <c r="A55">
         <v>67</v>
       </c>
+      <c r="B55" s="8" t="s">
+        <v>1343</v>
+      </c>
       <c r="C55" t="s">
         <v>574</v>
       </c>
@@ -7035,6 +7594,9 @@
       <c r="A56">
         <v>68</v>
       </c>
+      <c r="B56" s="8" t="s">
+        <v>1344</v>
+      </c>
       <c r="C56" t="s">
         <v>575</v>
       </c>
@@ -7063,6 +7625,9 @@
       <c r="A57">
         <v>69</v>
       </c>
+      <c r="B57" s="8" t="s">
+        <v>1345</v>
+      </c>
       <c r="C57" t="s">
         <v>576</v>
       </c>
@@ -7091,6 +7656,9 @@
       <c r="A58">
         <v>72</v>
       </c>
+      <c r="B58" s="8" t="s">
+        <v>1346</v>
+      </c>
       <c r="C58" t="s">
         <v>577</v>
       </c>
@@ -7119,6 +7687,9 @@
       <c r="A59">
         <v>73</v>
       </c>
+      <c r="B59" s="8" t="s">
+        <v>1347</v>
+      </c>
       <c r="C59" t="s">
         <v>578</v>
       </c>
@@ -7147,6 +7718,9 @@
       <c r="A60">
         <v>75</v>
       </c>
+      <c r="B60" s="8" t="s">
+        <v>1348</v>
+      </c>
       <c r="C60" t="s">
         <v>7</v>
       </c>
@@ -7175,6 +7749,9 @@
       <c r="A61">
         <v>77</v>
       </c>
+      <c r="B61" s="8" t="s">
+        <v>1349</v>
+      </c>
       <c r="C61" t="s">
         <v>6</v>
       </c>
@@ -7202,6 +7779,9 @@
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>78</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>1350</v>
       </c>
       <c r="C62" t="s">
         <v>579</v>
@@ -7221,6 +7801,9 @@
       <c r="A63">
         <v>82</v>
       </c>
+      <c r="B63" s="8" t="s">
+        <v>1351</v>
+      </c>
       <c r="C63" t="s">
         <v>580</v>
       </c>
@@ -7249,6 +7832,9 @@
       <c r="A64">
         <v>83</v>
       </c>
+      <c r="B64" s="8" t="s">
+        <v>1353</v>
+      </c>
       <c r="C64" t="s">
         <v>581</v>
       </c>
@@ -7277,6 +7863,9 @@
       <c r="A65">
         <v>84</v>
       </c>
+      <c r="B65" s="8" t="s">
+        <v>1354</v>
+      </c>
       <c r="C65" t="s">
         <v>582</v>
       </c>
@@ -7305,6 +7894,9 @@
       <c r="A66">
         <v>85</v>
       </c>
+      <c r="B66" s="8" t="s">
+        <v>1355</v>
+      </c>
       <c r="C66" t="s">
         <v>583</v>
       </c>
@@ -7333,6 +7925,9 @@
       <c r="A67">
         <v>86</v>
       </c>
+      <c r="B67" s="8" t="s">
+        <v>1356</v>
+      </c>
       <c r="C67" t="s">
         <v>584</v>
       </c>
@@ -7361,6 +7956,9 @@
       <c r="A68">
         <v>87</v>
       </c>
+      <c r="B68" s="8" t="s">
+        <v>1352</v>
+      </c>
       <c r="C68" t="s">
         <v>585</v>
       </c>
@@ -7389,6 +7987,9 @@
       <c r="A69">
         <v>88</v>
       </c>
+      <c r="B69" s="8" t="s">
+        <v>1357</v>
+      </c>
       <c r="C69" t="s">
         <v>586</v>
       </c>
@@ -7417,6 +8018,9 @@
       <c r="A70">
         <v>100</v>
       </c>
+      <c r="B70" s="8" t="s">
+        <v>1358</v>
+      </c>
       <c r="C70" t="s">
         <v>587</v>
       </c>
@@ -7445,6 +8049,9 @@
       <c r="A71">
         <v>102</v>
       </c>
+      <c r="B71" s="8" t="s">
+        <v>1359</v>
+      </c>
       <c r="C71" t="s">
         <v>589</v>
       </c>
@@ -7473,6 +8080,9 @@
       <c r="A72">
         <v>103</v>
       </c>
+      <c r="B72" s="8" t="s">
+        <v>1360</v>
+      </c>
       <c r="C72" t="s">
         <v>590</v>
       </c>
@@ -7501,6 +8111,9 @@
       <c r="A73">
         <v>106</v>
       </c>
+      <c r="B73" s="8" t="s">
+        <v>1361</v>
+      </c>
       <c r="C73" t="s">
         <v>591</v>
       </c>
@@ -7528,6 +8141,9 @@
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>107</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>1362</v>
       </c>
       <c r="C74" t="s">
         <v>592</v>
@@ -7547,6 +8163,9 @@
       <c r="A75">
         <v>108</v>
       </c>
+      <c r="B75" s="8" t="s">
+        <v>1363</v>
+      </c>
       <c r="C75" t="s">
         <v>593</v>
       </c>
@@ -7575,6 +8194,9 @@
       <c r="A76">
         <v>109</v>
       </c>
+      <c r="B76" s="8" t="s">
+        <v>1364</v>
+      </c>
       <c r="C76" t="s">
         <v>594</v>
       </c>
@@ -7603,6 +8225,9 @@
       <c r="A77">
         <v>110</v>
       </c>
+      <c r="B77" s="8" t="s">
+        <v>1365</v>
+      </c>
       <c r="C77" t="s">
         <v>595</v>
       </c>
@@ -7631,6 +8256,9 @@
       <c r="A78">
         <v>112</v>
       </c>
+      <c r="B78" s="8" t="s">
+        <v>1366</v>
+      </c>
       <c r="C78" t="s">
         <v>596</v>
       </c>
@@ -7659,6 +8287,9 @@
       <c r="A79">
         <v>113</v>
       </c>
+      <c r="B79" s="8" t="s">
+        <v>1367</v>
+      </c>
       <c r="C79" t="s">
         <v>597</v>
       </c>
@@ -7687,6 +8318,9 @@
       <c r="A80">
         <v>114</v>
       </c>
+      <c r="B80" s="8" t="s">
+        <v>1368</v>
+      </c>
       <c r="C80" t="s">
         <v>598</v>
       </c>
@@ -7715,6 +8349,9 @@
       <c r="A81">
         <v>115</v>
       </c>
+      <c r="B81" s="8" t="s">
+        <v>1369</v>
+      </c>
       <c r="C81" t="s">
         <v>599</v>
       </c>
@@ -7743,6 +8380,9 @@
       <c r="A82">
         <v>116</v>
       </c>
+      <c r="B82" s="8" t="s">
+        <v>1370</v>
+      </c>
       <c r="C82" t="s">
         <v>600</v>
       </c>
@@ -7771,6 +8411,9 @@
       <c r="A83">
         <v>117</v>
       </c>
+      <c r="B83" s="8" t="s">
+        <v>1371</v>
+      </c>
       <c r="C83" t="s">
         <v>601</v>
       </c>
@@ -7799,6 +8442,9 @@
       <c r="A84">
         <v>118</v>
       </c>
+      <c r="B84" s="8" t="s">
+        <v>1372</v>
+      </c>
       <c r="C84" t="s">
         <v>602</v>
       </c>
@@ -7827,6 +8473,9 @@
       <c r="A85">
         <v>119</v>
       </c>
+      <c r="B85" s="8" t="s">
+        <v>1373</v>
+      </c>
       <c r="C85" t="s">
         <v>603</v>
       </c>
@@ -7855,6 +8504,9 @@
       <c r="A86">
         <v>121</v>
       </c>
+      <c r="B86" s="8" t="s">
+        <v>1374</v>
+      </c>
       <c r="C86" t="s">
         <v>604</v>
       </c>
@@ -7883,6 +8535,9 @@
       <c r="A87">
         <v>122</v>
       </c>
+      <c r="B87" s="8" t="s">
+        <v>1375</v>
+      </c>
       <c r="C87" t="s">
         <v>605</v>
       </c>
@@ -7911,6 +8566,9 @@
       <c r="A88">
         <v>124</v>
       </c>
+      <c r="B88" s="8" t="s">
+        <v>1376</v>
+      </c>
       <c r="C88" t="s">
         <v>606</v>
       </c>
@@ -7939,6 +8597,9 @@
       <c r="A89">
         <v>125</v>
       </c>
+      <c r="B89" s="8" t="s">
+        <v>1378</v>
+      </c>
       <c r="C89" t="s">
         <v>607</v>
       </c>
@@ -7967,6 +8628,9 @@
       <c r="A90">
         <v>128</v>
       </c>
+      <c r="B90" s="8" t="s">
+        <v>1377</v>
+      </c>
       <c r="C90" t="s">
         <v>608</v>
       </c>
@@ -7995,6 +8659,9 @@
       <c r="A91">
         <v>129</v>
       </c>
+      <c r="B91" s="8" t="s">
+        <v>1380</v>
+      </c>
       <c r="C91" t="s">
         <v>609</v>
       </c>
@@ -8023,6 +8690,9 @@
       <c r="A92">
         <v>130</v>
       </c>
+      <c r="B92" s="8" t="s">
+        <v>1381</v>
+      </c>
       <c r="C92" t="s">
         <v>610</v>
       </c>
@@ -8051,6 +8721,9 @@
       <c r="A93">
         <v>131</v>
       </c>
+      <c r="B93" s="8" t="s">
+        <v>1382</v>
+      </c>
       <c r="C93" t="s">
         <v>611</v>
       </c>
@@ -8079,6 +8752,9 @@
       <c r="A94">
         <v>132</v>
       </c>
+      <c r="B94" s="8" t="s">
+        <v>1383</v>
+      </c>
       <c r="C94" t="s">
         <v>612</v>
       </c>
@@ -8107,6 +8783,9 @@
       <c r="A95">
         <v>133</v>
       </c>
+      <c r="B95" s="8" t="s">
+        <v>1384</v>
+      </c>
       <c r="C95" t="s">
         <v>613</v>
       </c>
@@ -8135,6 +8814,9 @@
       <c r="A96">
         <v>134</v>
       </c>
+      <c r="B96" s="8" t="s">
+        <v>1385</v>
+      </c>
       <c r="C96" t="s">
         <v>614</v>
       </c>
@@ -8163,6 +8845,9 @@
       <c r="A97">
         <v>135</v>
       </c>
+      <c r="B97" s="8" t="s">
+        <v>1386</v>
+      </c>
       <c r="C97" t="s">
         <v>615</v>
       </c>
@@ -8191,6 +8876,9 @@
       <c r="A98">
         <v>136</v>
       </c>
+      <c r="B98" s="8" t="s">
+        <v>1387</v>
+      </c>
       <c r="C98" t="s">
         <v>616</v>
       </c>
@@ -8219,6 +8907,9 @@
       <c r="A99">
         <v>137</v>
       </c>
+      <c r="B99" s="8" t="s">
+        <v>1388</v>
+      </c>
       <c r="C99" t="s">
         <v>617</v>
       </c>
@@ -8247,6 +8938,9 @@
       <c r="A100">
         <v>138</v>
       </c>
+      <c r="B100" s="8" t="s">
+        <v>1389</v>
+      </c>
       <c r="C100" t="s">
         <v>618</v>
       </c>
@@ -8275,6 +8969,9 @@
       <c r="A101">
         <v>139</v>
       </c>
+      <c r="B101" s="8" t="s">
+        <v>1390</v>
+      </c>
       <c r="C101" t="s">
         <v>619</v>
       </c>
@@ -8303,6 +9000,9 @@
       <c r="A102">
         <v>140</v>
       </c>
+      <c r="B102" s="8" t="s">
+        <v>1391</v>
+      </c>
       <c r="C102" t="s">
         <v>620</v>
       </c>
@@ -8331,6 +9031,9 @@
       <c r="A103">
         <v>141</v>
       </c>
+      <c r="B103" s="8" t="s">
+        <v>1392</v>
+      </c>
       <c r="C103" t="s">
         <v>621</v>
       </c>
@@ -8359,6 +9062,9 @@
       <c r="A104">
         <v>142</v>
       </c>
+      <c r="B104" s="8" t="s">
+        <v>1393</v>
+      </c>
       <c r="C104" t="s">
         <v>622</v>
       </c>
@@ -8387,6 +9093,9 @@
       <c r="A105">
         <v>143</v>
       </c>
+      <c r="B105" s="8" t="s">
+        <v>1394</v>
+      </c>
       <c r="C105" t="s">
         <v>623</v>
       </c>
@@ -8415,6 +9124,9 @@
       <c r="A106">
         <v>144</v>
       </c>
+      <c r="B106" s="8" t="s">
+        <v>1395</v>
+      </c>
       <c r="C106" t="s">
         <v>624</v>
       </c>
@@ -8443,6 +9155,9 @@
       <c r="A107">
         <v>145</v>
       </c>
+      <c r="B107" s="8" t="s">
+        <v>1396</v>
+      </c>
       <c r="C107" t="s">
         <v>625</v>
       </c>
@@ -8471,6 +9186,9 @@
       <c r="A108">
         <v>146</v>
       </c>
+      <c r="B108" s="8" t="s">
+        <v>1397</v>
+      </c>
       <c r="C108" t="s">
         <v>626</v>
       </c>
@@ -8499,6 +9217,9 @@
       <c r="A109">
         <v>148</v>
       </c>
+      <c r="B109" s="8" t="s">
+        <v>1398</v>
+      </c>
       <c r="C109" t="s">
         <v>627</v>
       </c>
@@ -8527,6 +9248,9 @@
       <c r="A110">
         <v>149</v>
       </c>
+      <c r="B110" s="8" t="s">
+        <v>1399</v>
+      </c>
       <c r="C110" t="s">
         <v>628</v>
       </c>
@@ -8554,6 +9278,9 @@
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>152</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>1379</v>
       </c>
       <c r="C111" t="s">
         <v>629</v>
@@ -8573,6 +9300,9 @@
       <c r="A112">
         <v>153</v>
       </c>
+      <c r="B112" s="8" t="s">
+        <v>1400</v>
+      </c>
       <c r="C112" t="s">
         <v>630</v>
       </c>
@@ -8591,6 +9321,9 @@
       <c r="A113">
         <v>154</v>
       </c>
+      <c r="B113" s="8" t="s">
+        <v>1401</v>
+      </c>
       <c r="C113" t="s">
         <v>631</v>
       </c>
@@ -8619,6 +9352,9 @@
       <c r="A114">
         <v>155</v>
       </c>
+      <c r="B114" s="8" t="s">
+        <v>1402</v>
+      </c>
       <c r="C114" t="s">
         <v>632</v>
       </c>
@@ -8647,6 +9383,9 @@
       <c r="A115">
         <v>156</v>
       </c>
+      <c r="B115" s="8" t="s">
+        <v>1403</v>
+      </c>
       <c r="C115" t="s">
         <v>633</v>
       </c>
@@ -8675,6 +9414,9 @@
       <c r="A116">
         <v>157</v>
       </c>
+      <c r="B116" s="8" t="s">
+        <v>1404</v>
+      </c>
       <c r="C116" t="s">
         <v>634</v>
       </c>
@@ -8703,6 +9445,9 @@
       <c r="A117">
         <v>158</v>
       </c>
+      <c r="B117" s="8" t="s">
+        <v>1405</v>
+      </c>
       <c r="C117" t="s">
         <v>635</v>
       </c>
@@ -8731,6 +9476,9 @@
       <c r="A118">
         <v>159</v>
       </c>
+      <c r="B118" s="8" t="s">
+        <v>1406</v>
+      </c>
       <c r="C118" t="s">
         <v>636</v>
       </c>
@@ -8759,6 +9507,9 @@
       <c r="A119">
         <v>160</v>
       </c>
+      <c r="B119" s="8" t="s">
+        <v>1407</v>
+      </c>
       <c r="C119" t="s">
         <v>637</v>
       </c>
@@ -8787,6 +9538,9 @@
       <c r="A120">
         <v>161</v>
       </c>
+      <c r="B120" s="8" t="s">
+        <v>1408</v>
+      </c>
       <c r="C120" t="s">
         <v>638</v>
       </c>
@@ -8815,6 +9569,9 @@
       <c r="A121">
         <v>162</v>
       </c>
+      <c r="B121" s="8" t="s">
+        <v>1409</v>
+      </c>
       <c r="C121" t="s">
         <v>639</v>
       </c>
@@ -8843,6 +9600,9 @@
       <c r="A122">
         <v>163</v>
       </c>
+      <c r="B122" s="8" t="s">
+        <v>1410</v>
+      </c>
       <c r="C122" t="s">
         <v>640</v>
       </c>
@@ -8871,6 +9631,9 @@
       <c r="A123">
         <v>164</v>
       </c>
+      <c r="B123" s="8" t="s">
+        <v>1411</v>
+      </c>
       <c r="C123" t="s">
         <v>641</v>
       </c>
@@ -8899,6 +9662,9 @@
       <c r="A124">
         <v>165</v>
       </c>
+      <c r="B124" s="8" t="s">
+        <v>1412</v>
+      </c>
       <c r="C124" t="s">
         <v>642</v>
       </c>
@@ -8927,6 +9693,9 @@
       <c r="A125">
         <v>166</v>
       </c>
+      <c r="B125" s="8" t="s">
+        <v>1413</v>
+      </c>
       <c r="C125" t="s">
         <v>643</v>
       </c>
@@ -8954,6 +9723,9 @@
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>167</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>1414</v>
       </c>
       <c r="C126" t="s">
         <v>644</v>
@@ -8973,6 +9745,9 @@
       <c r="A127">
         <v>168</v>
       </c>
+      <c r="B127" s="8" t="s">
+        <v>1415</v>
+      </c>
       <c r="C127" t="s">
         <v>645</v>
       </c>
@@ -9000,6 +9775,9 @@
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>169</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>1416</v>
       </c>
       <c r="C128" t="s">
         <v>646</v>
@@ -9019,6 +9797,9 @@
       <c r="A129">
         <v>170</v>
       </c>
+      <c r="B129" s="8" t="s">
+        <v>1417</v>
+      </c>
       <c r="C129" t="s">
         <v>647</v>
       </c>
@@ -9037,6 +9818,9 @@
       <c r="A130">
         <v>171</v>
       </c>
+      <c r="B130" s="8" t="s">
+        <v>1418</v>
+      </c>
       <c r="C130" t="s">
         <v>648</v>
       </c>
@@ -9055,6 +9839,9 @@
       <c r="A131">
         <v>172</v>
       </c>
+      <c r="B131" s="8" t="s">
+        <v>1419</v>
+      </c>
       <c r="C131" t="s">
         <v>649</v>
       </c>
@@ -9073,6 +9860,9 @@
       <c r="A132">
         <v>173</v>
       </c>
+      <c r="B132" s="8" t="s">
+        <v>1420</v>
+      </c>
       <c r="C132" t="s">
         <v>650</v>
       </c>
@@ -9100,6 +9890,9 @@
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>174</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>1421</v>
       </c>
       <c r="C133" t="s">
         <v>651</v>
@@ -9119,6 +9912,9 @@
       <c r="A134">
         <v>175</v>
       </c>
+      <c r="B134" s="8" t="s">
+        <v>1422</v>
+      </c>
       <c r="C134" t="s">
         <v>652</v>
       </c>
@@ -9137,6 +9933,9 @@
       <c r="A135">
         <v>176</v>
       </c>
+      <c r="B135" s="8" t="s">
+        <v>1423</v>
+      </c>
       <c r="C135" t="s">
         <v>653</v>
       </c>
@@ -9155,6 +9954,9 @@
       <c r="A136">
         <v>177</v>
       </c>
+      <c r="B136" s="8" t="s">
+        <v>1424</v>
+      </c>
       <c r="C136" t="s">
         <v>654</v>
       </c>
@@ -9173,7 +9975,7 @@
       <c r="A137">
         <v>178</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="8" t="s">
         <v>988</v>
       </c>
       <c r="C137" t="s">

--- a/data/excel_sql/3.-tables_db.xlsx
+++ b/data/excel_sql/3.-tables_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\excel_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\REDIM_1\data\excel_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7A414F-A511-4127-BAF8-F723F2B629F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849613C8-F3DA-402A-890C-5BBC249C9321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YEARS" sheetId="8" r:id="rId1"/>
@@ -19,21 +19,13 @@
     <sheet name="CATEGORIES" sheetId="14" r:id="rId4"/>
     <sheet name="CENTERS" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -4429,9 +4421,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="none">
@@ -4471,6 +4460,9 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4541,13 +4533,7 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}" name="Tabla5" displayName="Tabla5" ref="A1:K435" totalsRowShown="0">
-  <autoFilter ref="A1:K435" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K435" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J435">
     <sortCondition ref="A1:A435"/>
   </sortState>
@@ -4555,30 +4541,30 @@
     <tableColumn id="1" xr3:uid="{4C99E144-E72B-4E1E-A1B0-6EE3FE3B2E9B}" name="id"/>
     <tableColumn id="10" xr3:uid="{010B5077-EADB-4D64-B9D2-B1BE619927D4}" name="level"/>
     <tableColumn id="3" xr3:uid="{81FB6481-665F-4EC2-B18A-967202B37711}" name="name"/>
-    <tableColumn id="11" xr3:uid="{9F3B3332-6035-4CA2-A5D8-7A88B6B724FD}" name="upload" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{9F3B3332-6035-4CA2-A5D8-7A88B6B724FD}" name="upload" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{5C408E3F-7EA0-4A74-9045-F0386B32748F}" name="status"/>
-    <tableColumn id="8" xr3:uid="{13CC9401-93CE-4134-BBE7-7E87C69DE5BA}" name="num_fechas" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{13CC9401-93CE-4134-BBE7-7E87C69DE5BA}" name="num_fechas" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{6415267F-4AFB-4E4A-95AD-51A014CB2BD0}" name="rango_fechas"/>
-    <tableColumn id="5" xr3:uid="{1F40335B-FDB9-4DB2-8D9C-5270D6F3B67A}" name="value" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{813CBB08-1D3D-43A8-8DEA-157F6DDF6F5F}" name="rows_in" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{FE5A63A0-C348-4543-ABB3-F94D2481FABA}" name="rows_out" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{1C7B014A-CE1E-4453-A91D-203FC4529D4A}" name="Obs" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{1F40335B-FDB9-4DB2-8D9C-5270D6F3B67A}" name="value" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{813CBB08-1D3D-43A8-8DEA-157F6DDF6F5F}" name="rows_in" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{FE5A63A0-C348-4543-ABB3-F94D2481FABA}" name="rows_out" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{1C7B014A-CE1E-4453-A91D-203FC4529D4A}" name="Obs" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}" name="Tabla2" displayName="Tabla2" ref="B1:E421" totalsRowShown="0" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}" name="Tabla2" displayName="Tabla2" ref="B1:E421" totalsRowShown="0" dataDxfId="4">
   <autoFilter ref="B1:E421" xr:uid="{56FABD45-52FF-47F2-9800-CECF01EE8CC6}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E421">
     <sortCondition ref="C1:C421"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8AF95AAF-7C97-4030-8813-E5F15884669B}" name="Estados" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B4C15FDA-B2EC-4A1D-A81E-4B2725E564AF}" name="Centros" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{17CD0285-B341-43C7-8ACD-65A35D973F9E}" name="ID" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{A0FEF947-428C-44F8-B2A5-5E3ECB03347F}" name="LARGO" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{8AF95AAF-7C97-4030-8813-E5F15884669B}" name="Estados" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B4C15FDA-B2EC-4A1D-A81E-4B2725E564AF}" name="Centros" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{17CD0285-B341-43C7-8ACD-65A35D973F9E}" name="ID" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A0FEF947-428C-44F8-B2A5-5E3ECB03347F}" name="LARGO" dataDxfId="0">
       <calculatedColumnFormula>LEN(Tabla2[[#This Row],[Centros]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4853,9 +4839,9 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -4866,7 +4852,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4877,7 +4863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4888,7 +4874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4899,7 +4885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4910,7 +4896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4921,7 +4907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4932,7 +4918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4943,7 +4929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4954,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4965,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4976,7 +4962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4987,7 +4973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4998,7 +4984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5009,7 +4995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5020,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5031,7 +5017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5042,7 +5028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5053,7 +5039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5064,7 +5050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5075,7 +5061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5086,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5097,7 +5083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5108,7 +5094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5119,7 +5105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5130,7 +5116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5141,7 +5127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5166,13 +5152,13 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -5192,7 +5178,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5212,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5232,7 +5218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5252,7 +5238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5272,7 +5258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5292,7 +5278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5312,7 +5298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5332,7 +5318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5352,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5372,7 +5358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5392,7 +5378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5412,7 +5398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5432,7 +5418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5452,7 +5438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5472,7 +5458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5492,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5512,7 +5498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5532,7 +5518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5552,7 +5538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5572,7 +5558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5592,7 +5578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5612,7 +5598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5632,7 +5618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5652,7 +5638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5672,7 +5658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5692,7 +5678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5712,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5732,7 +5718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5752,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5772,7 +5758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5792,7 +5778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5812,7 +5798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5846,12 +5832,12 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -5862,7 +5848,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5873,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5884,7 +5870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5895,7 +5881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5906,7 +5892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5931,19 +5917,19 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:K435"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="41.6640625" customWidth="1"/>
-    <col min="8" max="10" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="41.7109375" customWidth="1"/>
+    <col min="8" max="10" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -5978,7 +5964,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6009,7 +5995,7 @@
       </c>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6040,7 +6026,7 @@
       </c>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6071,7 +6057,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -6102,7 +6088,7 @@
       </c>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -6132,7 +6118,7 @@
       </c>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -6162,7 +6148,7 @@
       </c>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -6192,7 +6178,7 @@
       </c>
       <c r="K8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>10</v>
       </c>
@@ -6222,7 +6208,7 @@
       </c>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -6240,7 +6226,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -6270,7 +6256,7 @@
       </c>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -6300,7 +6286,7 @@
       </c>
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -6330,7 +6316,7 @@
       </c>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
@@ -6360,7 +6346,7 @@
       </c>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
@@ -6378,7 +6364,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>19</v>
       </c>
@@ -6408,7 +6394,7 @@
       </c>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20</v>
       </c>
@@ -6438,7 +6424,7 @@
       </c>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
@@ -6468,7 +6454,7 @@
       </c>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>23</v>
       </c>
@@ -6498,7 +6484,7 @@
       </c>
       <c r="K19" s="3"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>24</v>
       </c>
@@ -6528,7 +6514,7 @@
       </c>
       <c r="K20" s="3"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>27</v>
       </c>
@@ -6558,7 +6544,7 @@
       </c>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>28</v>
       </c>
@@ -6588,7 +6574,7 @@
       </c>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>29</v>
       </c>
@@ -6618,7 +6604,7 @@
       </c>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>30</v>
       </c>
@@ -6648,7 +6634,7 @@
       </c>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>31</v>
       </c>
@@ -6666,7 +6652,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="3"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>32</v>
       </c>
@@ -6696,7 +6682,7 @@
       </c>
       <c r="K26" s="3"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>33</v>
       </c>
@@ -6726,7 +6712,7 @@
       </c>
       <c r="K27" s="3"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>34</v>
       </c>
@@ -6756,7 +6742,7 @@
       </c>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>35</v>
       </c>
@@ -6774,7 +6760,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>36</v>
       </c>
@@ -6804,7 +6790,7 @@
       </c>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>37</v>
       </c>
@@ -6822,7 +6808,7 @@
       <c r="J31" s="6"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>38</v>
       </c>
@@ -6840,7 +6826,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="3"/>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>39</v>
       </c>
@@ -6858,7 +6844,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>40</v>
       </c>
@@ -6888,7 +6874,7 @@
       </c>
       <c r="K34" s="3"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>41</v>
       </c>
@@ -6918,7 +6904,7 @@
       </c>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>43</v>
       </c>
@@ -6948,7 +6934,7 @@
       </c>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>44</v>
       </c>
@@ -6978,7 +6964,7 @@
       </c>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>46</v>
       </c>
@@ -7008,7 +6994,7 @@
       </c>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>47</v>
       </c>
@@ -7038,7 +7024,7 @@
       </c>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>48</v>
       </c>
@@ -7068,7 +7054,7 @@
       </c>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>49</v>
       </c>
@@ -7098,7 +7084,7 @@
       </c>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>50</v>
       </c>
@@ -7128,7 +7114,7 @@
       </c>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>51</v>
       </c>
@@ -7158,7 +7144,7 @@
       </c>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>52</v>
       </c>
@@ -7188,7 +7174,7 @@
       </c>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>53</v>
       </c>
@@ -7218,7 +7204,7 @@
       </c>
       <c r="K45" s="3"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>56</v>
       </c>
@@ -7248,7 +7234,7 @@
       </c>
       <c r="K46" s="3"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>57</v>
       </c>
@@ -7278,7 +7264,7 @@
       </c>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>58</v>
       </c>
@@ -7296,7 +7282,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="3"/>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>59</v>
       </c>
@@ -7314,7 +7300,7 @@
       <c r="J49" s="4"/>
       <c r="K49" s="3"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>60</v>
       </c>
@@ -7344,7 +7330,7 @@
       </c>
       <c r="K50" s="3"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>63</v>
       </c>
@@ -7374,7 +7360,7 @@
       </c>
       <c r="K51" s="3"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>64</v>
       </c>
@@ -7404,7 +7390,7 @@
       </c>
       <c r="K52" s="3"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>65</v>
       </c>
@@ -7434,7 +7420,7 @@
       </c>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>66</v>
       </c>
@@ -7464,7 +7450,7 @@
       </c>
       <c r="K54" s="3"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>67</v>
       </c>
@@ -7494,7 +7480,7 @@
       </c>
       <c r="K55" s="3"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>68</v>
       </c>
@@ -7524,7 +7510,7 @@
       </c>
       <c r="K56" s="3"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>69</v>
       </c>
@@ -7554,7 +7540,7 @@
       </c>
       <c r="K57" s="3"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>72</v>
       </c>
@@ -7584,7 +7570,7 @@
       </c>
       <c r="K58" s="3"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>73</v>
       </c>
@@ -7614,7 +7600,7 @@
       </c>
       <c r="K59" s="3"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>75</v>
       </c>
@@ -7644,7 +7630,7 @@
       </c>
       <c r="K60" s="3"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>77</v>
       </c>
@@ -7674,7 +7660,7 @@
       </c>
       <c r="K61" s="3"/>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>78</v>
       </c>
@@ -7692,7 +7678,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="3"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>82</v>
       </c>
@@ -7722,7 +7708,7 @@
       </c>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>83</v>
       </c>
@@ -7752,7 +7738,7 @@
       </c>
       <c r="K64" s="3"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>84</v>
       </c>
@@ -7782,7 +7768,7 @@
       </c>
       <c r="K65" s="3"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>85</v>
       </c>
@@ -7812,7 +7798,7 @@
       </c>
       <c r="K66" s="3"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>86</v>
       </c>
@@ -7842,7 +7828,7 @@
       </c>
       <c r="K67" s="3"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>87</v>
       </c>
@@ -7872,7 +7858,7 @@
       </c>
       <c r="K68" s="3"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>88</v>
       </c>
@@ -7902,7 +7888,7 @@
       </c>
       <c r="K69" s="3"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>100</v>
       </c>
@@ -7932,7 +7918,7 @@
       </c>
       <c r="K70" s="3"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>102</v>
       </c>
@@ -7962,7 +7948,7 @@
       </c>
       <c r="K71" s="3"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>103</v>
       </c>
@@ -7992,7 +7978,7 @@
       </c>
       <c r="K72" s="3"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>106</v>
       </c>
@@ -8022,7 +8008,7 @@
       </c>
       <c r="K73" s="3"/>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>107</v>
       </c>
@@ -8040,7 +8026,7 @@
       <c r="J74" s="6"/>
       <c r="K74" s="3"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>108</v>
       </c>
@@ -8070,7 +8056,7 @@
       </c>
       <c r="K75" s="3"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>109</v>
       </c>
@@ -8100,7 +8086,7 @@
       </c>
       <c r="K76" s="3"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>110</v>
       </c>
@@ -8130,7 +8116,7 @@
       </c>
       <c r="K77" s="3"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>112</v>
       </c>
@@ -8160,7 +8146,7 @@
       </c>
       <c r="K78" s="3"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>113</v>
       </c>
@@ -8190,7 +8176,7 @@
       </c>
       <c r="K79" s="3"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>114</v>
       </c>
@@ -8220,7 +8206,7 @@
       </c>
       <c r="K80" s="3"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>115</v>
       </c>
@@ -8250,7 +8236,7 @@
       </c>
       <c r="K81" s="3"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>116</v>
       </c>
@@ -8280,7 +8266,7 @@
       </c>
       <c r="K82" s="3"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>117</v>
       </c>
@@ -8310,7 +8296,7 @@
       </c>
       <c r="K83" s="3"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>118</v>
       </c>
@@ -8340,7 +8326,7 @@
       </c>
       <c r="K84" s="3"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>119</v>
       </c>
@@ -8370,7 +8356,7 @@
       </c>
       <c r="K85" s="3"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>121</v>
       </c>
@@ -8400,7 +8386,7 @@
       </c>
       <c r="K86" s="3"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>122</v>
       </c>
@@ -8430,7 +8416,7 @@
       </c>
       <c r="K87" s="3"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>124</v>
       </c>
@@ -8460,7 +8446,7 @@
       </c>
       <c r="K88" s="3"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>125</v>
       </c>
@@ -8490,7 +8476,7 @@
       </c>
       <c r="K89" s="3"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>128</v>
       </c>
@@ -8520,7 +8506,7 @@
       </c>
       <c r="K90" s="3"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>129</v>
       </c>
@@ -8550,7 +8536,7 @@
       </c>
       <c r="K91" s="3"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>130</v>
       </c>
@@ -8580,7 +8566,7 @@
       </c>
       <c r="K92" s="3"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>131</v>
       </c>
@@ -8610,7 +8596,7 @@
       </c>
       <c r="K93" s="3"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>132</v>
       </c>
@@ -8640,7 +8626,7 @@
       </c>
       <c r="K94" s="3"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>133</v>
       </c>
@@ -8670,7 +8656,7 @@
       </c>
       <c r="K95" s="3"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>134</v>
       </c>
@@ -8700,7 +8686,7 @@
       </c>
       <c r="K96" s="3"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>135</v>
       </c>
@@ -8730,7 +8716,7 @@
       </c>
       <c r="K97" s="3"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>136</v>
       </c>
@@ -8760,7 +8746,7 @@
       </c>
       <c r="K98" s="3"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>137</v>
       </c>
@@ -8790,7 +8776,7 @@
       </c>
       <c r="K99" s="3"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>138</v>
       </c>
@@ -8820,7 +8806,7 @@
       </c>
       <c r="K100" s="3"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>139</v>
       </c>
@@ -8850,7 +8836,7 @@
       </c>
       <c r="K101" s="3"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>140</v>
       </c>
@@ -8880,7 +8866,7 @@
       </c>
       <c r="K102" s="3"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>141</v>
       </c>
@@ -8910,7 +8896,7 @@
       </c>
       <c r="K103" s="3"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>142</v>
       </c>
@@ -8940,7 +8926,7 @@
       </c>
       <c r="K104" s="3"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>143</v>
       </c>
@@ -8970,7 +8956,7 @@
       </c>
       <c r="K105" s="3"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>144</v>
       </c>
@@ -9000,7 +8986,7 @@
       </c>
       <c r="K106" s="3"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>145</v>
       </c>
@@ -9030,7 +9016,7 @@
       </c>
       <c r="K107" s="3"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>146</v>
       </c>
@@ -9060,7 +9046,7 @@
       </c>
       <c r="K108" s="3"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>148</v>
       </c>
@@ -9090,7 +9076,7 @@
       </c>
       <c r="K109" s="3"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>149</v>
       </c>
@@ -9120,7 +9106,7 @@
       </c>
       <c r="K110" s="3"/>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>152</v>
       </c>
@@ -9138,7 +9124,7 @@
       <c r="J111" s="4"/>
       <c r="K111" s="3"/>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>153</v>
       </c>
@@ -9156,7 +9142,7 @@
       <c r="J112" s="4"/>
       <c r="K112" s="3"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>154</v>
       </c>
@@ -9186,7 +9172,7 @@
       </c>
       <c r="K113" s="3"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>155</v>
       </c>
@@ -9216,7 +9202,7 @@
       </c>
       <c r="K114" s="3"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>156</v>
       </c>
@@ -9246,7 +9232,7 @@
       </c>
       <c r="K115" s="3"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>157</v>
       </c>
@@ -9276,7 +9262,7 @@
       </c>
       <c r="K116" s="3"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>158</v>
       </c>
@@ -9306,7 +9292,7 @@
       </c>
       <c r="K117" s="3"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>159</v>
       </c>
@@ -9336,7 +9322,7 @@
       </c>
       <c r="K118" s="3"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>160</v>
       </c>
@@ -9366,7 +9352,7 @@
       </c>
       <c r="K119" s="3"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>161</v>
       </c>
@@ -9396,7 +9382,7 @@
       </c>
       <c r="K120" s="3"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>162</v>
       </c>
@@ -9426,7 +9412,7 @@
       </c>
       <c r="K121" s="3"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>163</v>
       </c>
@@ -9456,7 +9442,7 @@
       </c>
       <c r="K122" s="3"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>164</v>
       </c>
@@ -9486,7 +9472,7 @@
       </c>
       <c r="K123" s="3"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>165</v>
       </c>
@@ -9516,7 +9502,7 @@
       </c>
       <c r="K124" s="3"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>166</v>
       </c>
@@ -9546,7 +9532,7 @@
       </c>
       <c r="K125" s="3"/>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>167</v>
       </c>
@@ -9564,7 +9550,7 @@
       <c r="J126" s="6"/>
       <c r="K126" s="3"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>168</v>
       </c>
@@ -9594,7 +9580,7 @@
       </c>
       <c r="K127" s="3"/>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>169</v>
       </c>
@@ -9612,7 +9598,7 @@
       <c r="J128" s="4"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>170</v>
       </c>
@@ -9630,7 +9616,7 @@
       <c r="J129" s="4"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>171</v>
       </c>
@@ -9648,7 +9634,7 @@
       <c r="J130" s="4"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>172</v>
       </c>
@@ -9666,7 +9652,7 @@
       <c r="J131" s="4"/>
       <c r="K131" s="3"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>173</v>
       </c>
@@ -9696,7 +9682,7 @@
       </c>
       <c r="K132" s="3"/>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>174</v>
       </c>
@@ -9714,7 +9700,7 @@
       <c r="J133" s="4"/>
       <c r="K133" s="3"/>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>175</v>
       </c>
@@ -9732,7 +9718,7 @@
       <c r="J134" s="4"/>
       <c r="K134" s="3"/>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>176</v>
       </c>
@@ -9750,7 +9736,7 @@
       <c r="J135" s="4"/>
       <c r="K135" s="3"/>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>177</v>
       </c>
@@ -9768,7 +9754,7 @@
       <c r="J136" s="4"/>
       <c r="K136" s="3"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>178</v>
       </c>
@@ -9798,7 +9784,7 @@
       </c>
       <c r="K137" s="3"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>179</v>
       </c>
@@ -9828,7 +9814,7 @@
       </c>
       <c r="K138" s="3"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>180</v>
       </c>
@@ -9858,7 +9844,7 @@
       </c>
       <c r="K139" s="3"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>181</v>
       </c>
@@ -9888,7 +9874,7 @@
       </c>
       <c r="K140" s="3"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>182</v>
       </c>
@@ -9918,7 +9904,7 @@
       </c>
       <c r="K141" s="3"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>183</v>
       </c>
@@ -9948,7 +9934,7 @@
       </c>
       <c r="K142" s="3"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>184</v>
       </c>
@@ -9978,7 +9964,7 @@
       </c>
       <c r="K143" s="3"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>185</v>
       </c>
@@ -10008,7 +9994,7 @@
       </c>
       <c r="K144" s="3"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>186</v>
       </c>
@@ -10038,7 +10024,7 @@
       </c>
       <c r="K145" s="3"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>187</v>
       </c>
@@ -10068,7 +10054,7 @@
       </c>
       <c r="K146" s="3"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>188</v>
       </c>
@@ -10098,7 +10084,7 @@
       </c>
       <c r="K147" s="3"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>189</v>
       </c>
@@ -10128,7 +10114,7 @@
       </c>
       <c r="K148" s="3"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>190</v>
       </c>
@@ -10158,7 +10144,7 @@
       </c>
       <c r="K149" s="3"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>191</v>
       </c>
@@ -10188,7 +10174,7 @@
       </c>
       <c r="K150" s="3"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>192</v>
       </c>
@@ -10218,7 +10204,7 @@
       </c>
       <c r="K151" s="3"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>193</v>
       </c>
@@ -10248,7 +10234,7 @@
       </c>
       <c r="K152" s="3"/>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>195</v>
       </c>
@@ -10266,7 +10252,7 @@
       <c r="J153" s="4"/>
       <c r="K153" s="3"/>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>196</v>
       </c>
@@ -10284,7 +10270,7 @@
       <c r="J154" s="4"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>197</v>
       </c>
@@ -10302,7 +10288,7 @@
       <c r="J155" s="4"/>
       <c r="K155" s="3"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>199</v>
       </c>
@@ -10332,7 +10318,7 @@
       </c>
       <c r="K156" s="3"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>200</v>
       </c>
@@ -10362,7 +10348,7 @@
       </c>
       <c r="K157" s="3"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>205</v>
       </c>
@@ -10392,7 +10378,7 @@
       </c>
       <c r="K158" s="3"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>206</v>
       </c>
@@ -10422,7 +10408,7 @@
       </c>
       <c r="K159" s="3"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>207</v>
       </c>
@@ -10452,7 +10438,7 @@
       </c>
       <c r="K160" s="3"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>208</v>
       </c>
@@ -10482,7 +10468,7 @@
       </c>
       <c r="K161" s="3"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>209</v>
       </c>
@@ -10512,7 +10498,7 @@
       </c>
       <c r="K162" s="3"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>210</v>
       </c>
@@ -10542,7 +10528,7 @@
       </c>
       <c r="K163" s="3"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>211</v>
       </c>
@@ -10572,7 +10558,7 @@
       </c>
       <c r="K164" s="3"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>212</v>
       </c>
@@ -10602,7 +10588,7 @@
       </c>
       <c r="K165" s="3"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>213</v>
       </c>
@@ -10632,7 +10618,7 @@
       </c>
       <c r="K166" s="3"/>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>214</v>
       </c>
@@ -10650,7 +10636,7 @@
       <c r="J167" s="4"/>
       <c r="K167" s="3"/>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>215</v>
       </c>
@@ -10668,7 +10654,7 @@
       <c r="J168" s="4"/>
       <c r="K168" s="3"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>216</v>
       </c>
@@ -10698,7 +10684,7 @@
       </c>
       <c r="K169" s="3"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>217</v>
       </c>
@@ -10728,7 +10714,7 @@
       </c>
       <c r="K170" s="3"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>218</v>
       </c>
@@ -10758,7 +10744,7 @@
       </c>
       <c r="K171" s="3"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>219</v>
       </c>
@@ -10788,7 +10774,7 @@
       </c>
       <c r="K172" s="3"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>220</v>
       </c>
@@ -10818,7 +10804,7 @@
       </c>
       <c r="K173" s="3"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>221</v>
       </c>
@@ -10848,7 +10834,7 @@
       </c>
       <c r="K174" s="3"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>225</v>
       </c>
@@ -10878,7 +10864,7 @@
       </c>
       <c r="K175" s="3"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>226</v>
       </c>
@@ -10908,7 +10894,7 @@
       </c>
       <c r="K176" s="3"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>227</v>
       </c>
@@ -10938,7 +10924,7 @@
       </c>
       <c r="K177" s="3"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>228</v>
       </c>
@@ -10968,7 +10954,7 @@
       </c>
       <c r="K178" s="3"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>229</v>
       </c>
@@ -10998,7 +10984,7 @@
       </c>
       <c r="K179" s="3"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>230</v>
       </c>
@@ -11028,7 +11014,7 @@
       </c>
       <c r="K180" s="3"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>231</v>
       </c>
@@ -11058,7 +11044,7 @@
       </c>
       <c r="K181" s="3"/>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>232</v>
       </c>
@@ -11076,7 +11062,7 @@
       <c r="J182" s="4"/>
       <c r="K182" s="3"/>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>233</v>
       </c>
@@ -11094,7 +11080,7 @@
       <c r="J183" s="4"/>
       <c r="K183" s="3"/>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>234</v>
       </c>
@@ -11112,7 +11098,7 @@
       <c r="J184" s="4"/>
       <c r="K184" s="3"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>235</v>
       </c>
@@ -11142,7 +11128,7 @@
       </c>
       <c r="K185" s="3"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>236</v>
       </c>
@@ -11172,7 +11158,7 @@
       </c>
       <c r="K186" s="3"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>237</v>
       </c>
@@ -11202,7 +11188,7 @@
       </c>
       <c r="K187" s="3"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>238</v>
       </c>
@@ -11232,7 +11218,7 @@
       </c>
       <c r="K188" s="3"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>239</v>
       </c>
@@ -11262,7 +11248,7 @@
       </c>
       <c r="K189" s="3"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>240</v>
       </c>
@@ -11292,7 +11278,7 @@
       </c>
       <c r="K190" s="3"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>241</v>
       </c>
@@ -11322,7 +11308,7 @@
       </c>
       <c r="K191" s="3"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>242</v>
       </c>
@@ -11352,7 +11338,7 @@
       </c>
       <c r="K192" s="3"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>243</v>
       </c>
@@ -11382,7 +11368,7 @@
       </c>
       <c r="K193" s="3"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>244</v>
       </c>
@@ -11412,7 +11398,7 @@
       </c>
       <c r="K194" s="3"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>245</v>
       </c>
@@ -11442,7 +11428,7 @@
       </c>
       <c r="K195" s="3"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>246</v>
       </c>
@@ -11472,7 +11458,7 @@
       </c>
       <c r="K196" s="3"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>247</v>
       </c>
@@ -11502,7 +11488,7 @@
       </c>
       <c r="K197" s="3"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>248</v>
       </c>
@@ -11532,7 +11518,7 @@
       </c>
       <c r="K198" s="3"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>249</v>
       </c>
@@ -11562,7 +11548,7 @@
       </c>
       <c r="K199" s="3"/>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>250</v>
       </c>
@@ -11580,7 +11566,7 @@
       <c r="J200" s="4"/>
       <c r="K200" s="3"/>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>251</v>
       </c>
@@ -11598,7 +11584,7 @@
       <c r="J201" s="4"/>
       <c r="K201" s="3"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>252</v>
       </c>
@@ -11628,7 +11614,7 @@
       </c>
       <c r="K202" s="3"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>253</v>
       </c>
@@ -11658,7 +11644,7 @@
       </c>
       <c r="K203" s="3"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>254</v>
       </c>
@@ -11688,7 +11674,7 @@
       </c>
       <c r="K204" s="3"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>255</v>
       </c>
@@ -11718,7 +11704,7 @@
       </c>
       <c r="K205" s="3"/>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>256</v>
       </c>
@@ -11736,7 +11722,7 @@
       <c r="J206" s="4"/>
       <c r="K206" s="3"/>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>257</v>
       </c>
@@ -11754,7 +11740,7 @@
       <c r="J207" s="4"/>
       <c r="K207" s="3"/>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>258</v>
       </c>
@@ -11772,7 +11758,7 @@
       <c r="J208" s="4"/>
       <c r="K208" s="3"/>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>259</v>
       </c>
@@ -11790,7 +11776,7 @@
       <c r="J209" s="6"/>
       <c r="K209" s="3"/>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>260</v>
       </c>
@@ -11808,7 +11794,7 @@
       <c r="J210" s="4"/>
       <c r="K210" s="3"/>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>261</v>
       </c>
@@ -11826,7 +11812,7 @@
       <c r="J211" s="4"/>
       <c r="K211" s="3"/>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>262</v>
       </c>
@@ -11844,7 +11830,7 @@
       <c r="J212" s="4"/>
       <c r="K212" s="3"/>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>263</v>
       </c>
@@ -11862,7 +11848,7 @@
       <c r="J213" s="4"/>
       <c r="K213" s="3"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>264</v>
       </c>
@@ -11892,7 +11878,7 @@
       </c>
       <c r="K214" s="3"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>265</v>
       </c>
@@ -11922,7 +11908,7 @@
       </c>
       <c r="K215" s="3"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>266</v>
       </c>
@@ -11952,7 +11938,7 @@
       </c>
       <c r="K216" s="3"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>267</v>
       </c>
@@ -11982,7 +11968,7 @@
       </c>
       <c r="K217" s="3"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>268</v>
       </c>
@@ -12012,7 +11998,7 @@
       </c>
       <c r="K218" s="3"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>269</v>
       </c>
@@ -12042,7 +12028,7 @@
       </c>
       <c r="K219" s="3"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>270</v>
       </c>
@@ -12072,7 +12058,7 @@
       </c>
       <c r="K220" s="3"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>271</v>
       </c>
@@ -12102,7 +12088,7 @@
       </c>
       <c r="K221" s="3"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>272</v>
       </c>
@@ -12132,7 +12118,7 @@
       </c>
       <c r="K222" s="3"/>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>273</v>
       </c>
@@ -12150,7 +12136,7 @@
       <c r="J223" s="6"/>
       <c r="K223" s="3"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>274</v>
       </c>
@@ -12180,7 +12166,7 @@
       </c>
       <c r="K224" s="3"/>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>275</v>
       </c>
@@ -12198,7 +12184,7 @@
       <c r="J225" s="4"/>
       <c r="K225" s="3"/>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>276</v>
       </c>
@@ -12216,7 +12202,7 @@
       <c r="J226" s="4"/>
       <c r="K226" s="3"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>277</v>
       </c>
@@ -12246,7 +12232,7 @@
       </c>
       <c r="K227" s="3"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>278</v>
       </c>
@@ -12276,7 +12262,7 @@
       </c>
       <c r="K228" s="3"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>279</v>
       </c>
@@ -12306,7 +12292,7 @@
       </c>
       <c r="K229" s="3"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>280</v>
       </c>
@@ -12336,7 +12322,7 @@
       </c>
       <c r="K230" s="3"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>281</v>
       </c>
@@ -12366,7 +12352,7 @@
       </c>
       <c r="K231" s="3"/>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>282</v>
       </c>
@@ -12396,7 +12382,7 @@
       </c>
       <c r="K232" s="3"/>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>283</v>
       </c>
@@ -12426,7 +12412,7 @@
       </c>
       <c r="K233" s="3"/>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>284</v>
       </c>
@@ -12456,7 +12442,7 @@
       </c>
       <c r="K234" s="3"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>285</v>
       </c>
@@ -12486,7 +12472,7 @@
       </c>
       <c r="K235" s="3"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>286</v>
       </c>
@@ -12516,7 +12502,7 @@
       </c>
       <c r="K236" s="3"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>287</v>
       </c>
@@ -12546,7 +12532,7 @@
       </c>
       <c r="K237" s="3"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>288</v>
       </c>
@@ -12576,7 +12562,7 @@
       </c>
       <c r="K238" s="3"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>289</v>
       </c>
@@ -12606,7 +12592,7 @@
       </c>
       <c r="K239" s="3"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>290</v>
       </c>
@@ -12636,7 +12622,7 @@
       </c>
       <c r="K240" s="3"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>291</v>
       </c>
@@ -12666,7 +12652,7 @@
       </c>
       <c r="K241" s="3"/>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>292</v>
       </c>
@@ -12684,7 +12670,7 @@
       <c r="J242" s="4"/>
       <c r="K242" s="3"/>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>293</v>
       </c>
@@ -12702,7 +12688,7 @@
       <c r="J243" s="4"/>
       <c r="K243" s="3"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>294</v>
       </c>
@@ -12732,7 +12718,7 @@
       </c>
       <c r="K244" s="3"/>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>295</v>
       </c>
@@ -12750,7 +12736,7 @@
       <c r="J245" s="6"/>
       <c r="K245" s="3"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>296</v>
       </c>
@@ -12780,7 +12766,7 @@
       </c>
       <c r="K246" s="3"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>297</v>
       </c>
@@ -12810,7 +12796,7 @@
       </c>
       <c r="K247" s="3"/>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>298</v>
       </c>
@@ -12828,7 +12814,7 @@
       <c r="J248" s="4"/>
       <c r="K248" s="3"/>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>299</v>
       </c>
@@ -12846,7 +12832,7 @@
       <c r="J249" s="4"/>
       <c r="K249" s="3"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>300</v>
       </c>
@@ -12876,7 +12862,7 @@
       </c>
       <c r="K250" s="3"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>301</v>
       </c>
@@ -12906,7 +12892,7 @@
       </c>
       <c r="K251" s="3"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>302</v>
       </c>
@@ -12936,7 +12922,7 @@
       </c>
       <c r="K252" s="3"/>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>303</v>
       </c>
@@ -12954,7 +12940,7 @@
       <c r="J253" s="4"/>
       <c r="K253" s="3"/>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>304</v>
       </c>
@@ -12972,7 +12958,7 @@
       <c r="J254" s="4"/>
       <c r="K254" s="3"/>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>305</v>
       </c>
@@ -12990,7 +12976,7 @@
       <c r="J255" s="6"/>
       <c r="K255" s="3"/>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>306</v>
       </c>
@@ -13020,7 +13006,7 @@
       </c>
       <c r="K256" s="3"/>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>307</v>
       </c>
@@ -13038,7 +13024,7 @@
       <c r="J257" s="4"/>
       <c r="K257" s="3"/>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>308</v>
       </c>
@@ -13056,7 +13042,7 @@
       <c r="J258" s="4"/>
       <c r="K258" s="3"/>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>309</v>
       </c>
@@ -13086,7 +13072,7 @@
       </c>
       <c r="K259" s="3"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>310</v>
       </c>
@@ -13116,7 +13102,7 @@
       </c>
       <c r="K260" s="3"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>311</v>
       </c>
@@ -13146,7 +13132,7 @@
       </c>
       <c r="K261" s="3"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>312</v>
       </c>
@@ -13176,7 +13162,7 @@
       </c>
       <c r="K262" s="3"/>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>313</v>
       </c>
@@ -13206,7 +13192,7 @@
       </c>
       <c r="K263" s="3"/>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>314</v>
       </c>
@@ -13224,7 +13210,7 @@
       <c r="J264" s="4"/>
       <c r="K264" s="3"/>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>315</v>
       </c>
@@ -13242,7 +13228,7 @@
       <c r="J265" s="4"/>
       <c r="K265" s="3"/>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>316</v>
       </c>
@@ -13260,7 +13246,7 @@
       <c r="J266" s="4"/>
       <c r="K266" s="3"/>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>317</v>
       </c>
@@ -13278,7 +13264,7 @@
       <c r="J267" s="4"/>
       <c r="K267" s="3"/>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>318</v>
       </c>
@@ -13308,7 +13294,7 @@
       </c>
       <c r="K268" s="3"/>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>319</v>
       </c>
@@ -13338,7 +13324,7 @@
       </c>
       <c r="K269" s="3"/>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>320</v>
       </c>
@@ -13368,7 +13354,7 @@
       </c>
       <c r="K270" s="3"/>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>321</v>
       </c>
@@ -13398,7 +13384,7 @@
       </c>
       <c r="K271" s="3"/>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>322</v>
       </c>
@@ -13416,7 +13402,7 @@
       <c r="J272" s="4"/>
       <c r="K272" s="3"/>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>323</v>
       </c>
@@ -13434,7 +13420,7 @@
       <c r="J273" s="4"/>
       <c r="K273" s="3"/>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>324</v>
       </c>
@@ -13464,7 +13450,7 @@
       </c>
       <c r="K274" s="3"/>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>325</v>
       </c>
@@ -13494,7 +13480,7 @@
       </c>
       <c r="K275" s="3"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>326</v>
       </c>
@@ -13524,7 +13510,7 @@
       </c>
       <c r="K276" s="3"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>327</v>
       </c>
@@ -13554,7 +13540,7 @@
       </c>
       <c r="K277" s="3"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>328</v>
       </c>
@@ -13584,7 +13570,7 @@
       </c>
       <c r="K278" s="3"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>329</v>
       </c>
@@ -13614,7 +13600,7 @@
       </c>
       <c r="K279" s="3"/>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>331</v>
       </c>
@@ -13632,7 +13618,7 @@
       <c r="J280" s="6"/>
       <c r="K280" s="3"/>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>332</v>
       </c>
@@ -13650,7 +13636,7 @@
       <c r="J281" s="4"/>
       <c r="K281" s="3"/>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>333</v>
       </c>
@@ -13668,7 +13654,7 @@
       <c r="J282" s="4"/>
       <c r="K282" s="3"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>334</v>
       </c>
@@ -13698,7 +13684,7 @@
       </c>
       <c r="K283" s="3"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>335</v>
       </c>
@@ -13728,7 +13714,7 @@
       </c>
       <c r="K284" s="3"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>336</v>
       </c>
@@ -13758,7 +13744,7 @@
       </c>
       <c r="K285" s="3"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>337</v>
       </c>
@@ -13788,7 +13774,7 @@
       </c>
       <c r="K286" s="3"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>338</v>
       </c>
@@ -13818,7 +13804,7 @@
       </c>
       <c r="K287" s="3"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>339</v>
       </c>
@@ -13848,7 +13834,7 @@
       </c>
       <c r="K288" s="3"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>340</v>
       </c>
@@ -13878,7 +13864,7 @@
       </c>
       <c r="K289" s="3"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>341</v>
       </c>
@@ -13908,7 +13894,7 @@
       </c>
       <c r="K290" s="3"/>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>342</v>
       </c>
@@ -13938,7 +13924,7 @@
       </c>
       <c r="K291" s="3"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>343</v>
       </c>
@@ -13968,7 +13954,7 @@
       </c>
       <c r="K292" s="3"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>344</v>
       </c>
@@ -13998,7 +13984,7 @@
       </c>
       <c r="K293" s="3"/>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>345</v>
       </c>
@@ -14016,7 +14002,7 @@
       <c r="J294" s="4"/>
       <c r="K294" s="3"/>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>346</v>
       </c>
@@ -14034,7 +14020,7 @@
       <c r="J295" s="4"/>
       <c r="K295" s="3"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>347</v>
       </c>
@@ -14064,7 +14050,7 @@
       </c>
       <c r="K296" s="3"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>348</v>
       </c>
@@ -14094,7 +14080,7 @@
       </c>
       <c r="K297" s="3"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>349</v>
       </c>
@@ -14124,7 +14110,7 @@
       </c>
       <c r="K298" s="3"/>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>350</v>
       </c>
@@ -14142,7 +14128,7 @@
       <c r="J299" s="6"/>
       <c r="K299" s="3"/>
     </row>
-    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>351</v>
       </c>
@@ -14160,7 +14146,7 @@
       <c r="J300" s="6"/>
       <c r="K300" s="3"/>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>352</v>
       </c>
@@ -14178,7 +14164,7 @@
       <c r="J301" s="6"/>
       <c r="K301" s="3"/>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>353</v>
       </c>
@@ -14208,7 +14194,7 @@
       </c>
       <c r="K302" s="3"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>354</v>
       </c>
@@ -14238,7 +14224,7 @@
       </c>
       <c r="K303" s="3"/>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>355</v>
       </c>
@@ -14256,7 +14242,7 @@
       <c r="J304" s="6"/>
       <c r="K304" s="3"/>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>356</v>
       </c>
@@ -14286,7 +14272,7 @@
       </c>
       <c r="K305" s="3"/>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>357</v>
       </c>
@@ -14316,7 +14302,7 @@
       </c>
       <c r="K306" s="3"/>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>358</v>
       </c>
@@ -14346,7 +14332,7 @@
       </c>
       <c r="K307" s="3"/>
     </row>
-    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>359</v>
       </c>
@@ -14364,7 +14350,7 @@
       <c r="J308" s="6"/>
       <c r="K308" s="3"/>
     </row>
-    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>360</v>
       </c>
@@ -14382,7 +14368,7 @@
       <c r="J309" s="6"/>
       <c r="K309" s="3"/>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>361</v>
       </c>
@@ -14412,7 +14398,7 @@
       </c>
       <c r="K310" s="3"/>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>362</v>
       </c>
@@ -14442,7 +14428,7 @@
       </c>
       <c r="K311" s="3"/>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>363</v>
       </c>
@@ -14472,7 +14458,7 @@
       </c>
       <c r="K312" s="3"/>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>364</v>
       </c>
@@ -14502,7 +14488,7 @@
       </c>
       <c r="K313" s="3"/>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>365</v>
       </c>
@@ -14520,7 +14506,7 @@
       <c r="J314" s="4"/>
       <c r="K314" s="3"/>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>366</v>
       </c>
@@ -14538,7 +14524,7 @@
       <c r="J315" s="4"/>
       <c r="K315" s="3"/>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>367</v>
       </c>
@@ -14556,7 +14542,7 @@
       <c r="J316" s="6"/>
       <c r="K316" s="3"/>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>368</v>
       </c>
@@ -14574,7 +14560,7 @@
       <c r="J317" s="4"/>
       <c r="K317" s="3"/>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>369</v>
       </c>
@@ -14592,7 +14578,7 @@
       <c r="J318" s="4"/>
       <c r="K318" s="3"/>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>370</v>
       </c>
@@ -14610,7 +14596,7 @@
       <c r="J319" s="4"/>
       <c r="K319" s="3"/>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>371</v>
       </c>
@@ -14628,7 +14614,7 @@
       <c r="J320" s="4"/>
       <c r="K320" s="3"/>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>372</v>
       </c>
@@ -14646,7 +14632,7 @@
       <c r="J321" s="4"/>
       <c r="K321" s="3"/>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>373</v>
       </c>
@@ -14676,7 +14662,7 @@
       </c>
       <c r="K322" s="3"/>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>374</v>
       </c>
@@ -14706,7 +14692,7 @@
       </c>
       <c r="K323" s="3"/>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>375</v>
       </c>
@@ -14724,7 +14710,7 @@
       <c r="J324" s="4"/>
       <c r="K324" s="3"/>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>376</v>
       </c>
@@ -14742,7 +14728,7 @@
       <c r="J325" s="4"/>
       <c r="K325" s="3"/>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>377</v>
       </c>
@@ -14760,7 +14746,7 @@
       <c r="J326" s="4"/>
       <c r="K326" s="3"/>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>378</v>
       </c>
@@ -14778,7 +14764,7 @@
       <c r="J327" s="4"/>
       <c r="K327" s="3"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>379</v>
       </c>
@@ -14808,7 +14794,7 @@
       </c>
       <c r="K328" s="3"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>380</v>
       </c>
@@ -14838,7 +14824,7 @@
       </c>
       <c r="K329" s="3"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>381</v>
       </c>
@@ -14868,7 +14854,7 @@
       </c>
       <c r="K330" s="3"/>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>382</v>
       </c>
@@ -14898,7 +14884,7 @@
       </c>
       <c r="K331" s="3"/>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>383</v>
       </c>
@@ -14928,7 +14914,7 @@
       </c>
       <c r="K332" s="3"/>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>384</v>
       </c>
@@ -14958,7 +14944,7 @@
       </c>
       <c r="K333" s="3"/>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>385</v>
       </c>
@@ -14976,7 +14962,7 @@
       <c r="J334" s="6"/>
       <c r="K334" s="3"/>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>386</v>
       </c>
@@ -15006,7 +14992,7 @@
       </c>
       <c r="K335" s="3"/>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>387</v>
       </c>
@@ -15036,7 +15022,7 @@
       </c>
       <c r="K336" s="3"/>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>388</v>
       </c>
@@ -15066,7 +15052,7 @@
       </c>
       <c r="K337" s="3"/>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>389</v>
       </c>
@@ -15096,7 +15082,7 @@
       </c>
       <c r="K338" s="3"/>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>390</v>
       </c>
@@ -15126,7 +15112,7 @@
       </c>
       <c r="K339" s="3"/>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>391</v>
       </c>
@@ -15156,7 +15142,7 @@
       </c>
       <c r="K340" s="3"/>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>392</v>
       </c>
@@ -15186,7 +15172,7 @@
       </c>
       <c r="K341" s="3"/>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>393</v>
       </c>
@@ -15216,7 +15202,7 @@
       </c>
       <c r="K342" s="3"/>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>394</v>
       </c>
@@ -15246,7 +15232,7 @@
       </c>
       <c r="K343" s="3"/>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>395</v>
       </c>
@@ -15264,7 +15250,7 @@
       <c r="J344" s="4"/>
       <c r="K344" s="3"/>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>396</v>
       </c>
@@ -15282,7 +15268,7 @@
       <c r="J345" s="4"/>
       <c r="K345" s="3"/>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>397</v>
       </c>
@@ -15312,7 +15298,7 @@
       </c>
       <c r="K346" s="3"/>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>398</v>
       </c>
@@ -15342,7 +15328,7 @@
       </c>
       <c r="K347" s="3"/>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>399</v>
       </c>
@@ -15372,7 +15358,7 @@
       </c>
       <c r="K348" s="3"/>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>400</v>
       </c>
@@ -15402,7 +15388,7 @@
       </c>
       <c r="K349" s="3"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>401</v>
       </c>
@@ -15432,7 +15418,7 @@
       </c>
       <c r="K350" s="3"/>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>402</v>
       </c>
@@ -15450,7 +15436,7 @@
       <c r="J351" s="6"/>
       <c r="K351" s="3"/>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>403</v>
       </c>
@@ -15480,7 +15466,7 @@
       </c>
       <c r="K352" s="3"/>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>404</v>
       </c>
@@ -15510,7 +15496,7 @@
       </c>
       <c r="K353" s="3"/>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>405</v>
       </c>
@@ -15540,7 +15526,7 @@
       </c>
       <c r="K354" s="3"/>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>406</v>
       </c>
@@ -15570,7 +15556,7 @@
       </c>
       <c r="K355" s="3"/>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>407</v>
       </c>
@@ -15600,7 +15586,7 @@
       </c>
       <c r="K356" s="3"/>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>408</v>
       </c>
@@ -15630,7 +15616,7 @@
       </c>
       <c r="K357" s="3"/>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>409</v>
       </c>
@@ -15660,7 +15646,7 @@
       </c>
       <c r="K358" s="3"/>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>410</v>
       </c>
@@ -15690,7 +15676,7 @@
       </c>
       <c r="K359" s="3"/>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>411</v>
       </c>
@@ -15720,7 +15706,7 @@
       </c>
       <c r="K360" s="3"/>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>412</v>
       </c>
@@ -15750,7 +15736,7 @@
       </c>
       <c r="K361" s="3"/>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>413</v>
       </c>
@@ -15780,7 +15766,7 @@
       </c>
       <c r="K362" s="3"/>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>414</v>
       </c>
@@ -15810,7 +15796,7 @@
       </c>
       <c r="K363" s="3"/>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>415</v>
       </c>
@@ -15840,7 +15826,7 @@
       </c>
       <c r="K364" s="3"/>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>416</v>
       </c>
@@ -15870,7 +15856,7 @@
       </c>
       <c r="K365" s="3"/>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>417</v>
       </c>
@@ -15900,7 +15886,7 @@
       </c>
       <c r="K366" s="3"/>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>418</v>
       </c>
@@ -15930,7 +15916,7 @@
       </c>
       <c r="K367" s="3"/>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>419</v>
       </c>
@@ -15960,7 +15946,7 @@
       </c>
       <c r="K368" s="3"/>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>420</v>
       </c>
@@ -15990,7 +15976,7 @@
       </c>
       <c r="K369" s="3"/>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>421</v>
       </c>
@@ -16020,7 +16006,7 @@
       </c>
       <c r="K370" s="3"/>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>422</v>
       </c>
@@ -16050,7 +16036,7 @@
       </c>
       <c r="K371" s="3"/>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>423</v>
       </c>
@@ -16080,7 +16066,7 @@
       </c>
       <c r="K372" s="3"/>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>424</v>
       </c>
@@ -16110,7 +16096,7 @@
       </c>
       <c r="K373" s="3"/>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>425</v>
       </c>
@@ -16140,7 +16126,7 @@
       </c>
       <c r="K374" s="3"/>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>426</v>
       </c>
@@ -16170,7 +16156,7 @@
       </c>
       <c r="K375" s="3"/>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>427</v>
       </c>
@@ -16200,7 +16186,7 @@
       </c>
       <c r="K376" s="3"/>
     </row>
-    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>429</v>
       </c>
@@ -16218,7 +16204,7 @@
       <c r="J377" s="6"/>
       <c r="K377" s="3"/>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>430</v>
       </c>
@@ -16248,7 +16234,7 @@
       </c>
       <c r="K378" s="3"/>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>431</v>
       </c>
@@ -16278,7 +16264,7 @@
       </c>
       <c r="K379" s="3"/>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>432</v>
       </c>
@@ -16308,7 +16294,7 @@
       </c>
       <c r="K380" s="3"/>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>433</v>
       </c>
@@ -16338,7 +16324,7 @@
       </c>
       <c r="K381" s="3"/>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>434</v>
       </c>
@@ -16368,7 +16354,7 @@
       </c>
       <c r="K382" s="3"/>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>435</v>
       </c>
@@ -16398,7 +16384,7 @@
       </c>
       <c r="K383" s="3"/>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>436</v>
       </c>
@@ -16428,7 +16414,7 @@
       </c>
       <c r="K384" s="3"/>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>437</v>
       </c>
@@ -16458,7 +16444,7 @@
       </c>
       <c r="K385" s="3"/>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>438</v>
       </c>
@@ -16488,7 +16474,7 @@
       </c>
       <c r="K386" s="3"/>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>439</v>
       </c>
@@ -16518,7 +16504,7 @@
       </c>
       <c r="K387" s="3"/>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>440</v>
       </c>
@@ -16548,7 +16534,7 @@
       </c>
       <c r="K388" s="3"/>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>441</v>
       </c>
@@ -16578,7 +16564,7 @@
       </c>
       <c r="K389" s="3"/>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>442</v>
       </c>
@@ -16608,7 +16594,7 @@
       </c>
       <c r="K390" s="3"/>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>443</v>
       </c>
@@ -16638,7 +16624,7 @@
       </c>
       <c r="K391" s="3"/>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>444</v>
       </c>
@@ -16668,7 +16654,7 @@
       </c>
       <c r="K392" s="3"/>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>445</v>
       </c>
@@ -16698,7 +16684,7 @@
       </c>
       <c r="K393" s="3"/>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>446</v>
       </c>
@@ -16728,7 +16714,7 @@
       </c>
       <c r="K394" s="3"/>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>447</v>
       </c>
@@ -16758,7 +16744,7 @@
       </c>
       <c r="K395" s="3"/>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>448</v>
       </c>
@@ -16788,7 +16774,7 @@
       </c>
       <c r="K396" s="3"/>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>449</v>
       </c>
@@ -16818,7 +16804,7 @@
       </c>
       <c r="K397" s="3"/>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>450</v>
       </c>
@@ -16848,7 +16834,7 @@
       </c>
       <c r="K398" s="3"/>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>451</v>
       </c>
@@ -16878,7 +16864,7 @@
       </c>
       <c r="K399" s="3"/>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>452</v>
       </c>
@@ -16896,7 +16882,7 @@
       <c r="J400" s="4"/>
       <c r="K400" s="3"/>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>453</v>
       </c>
@@ -16926,7 +16912,7 @@
       </c>
       <c r="K401" s="3"/>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>454</v>
       </c>
@@ -16956,7 +16942,7 @@
       </c>
       <c r="K402" s="3"/>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>455</v>
       </c>
@@ -16974,7 +16960,7 @@
       <c r="J403" s="6"/>
       <c r="K403" s="3"/>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>456</v>
       </c>
@@ -17004,7 +16990,7 @@
       </c>
       <c r="K404" s="3"/>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>457</v>
       </c>
@@ -17022,7 +17008,7 @@
       <c r="J405" s="6"/>
       <c r="K405" s="3"/>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>458</v>
       </c>
@@ -17052,7 +17038,7 @@
       </c>
       <c r="K406" s="3"/>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>459</v>
       </c>
@@ -17082,7 +17068,7 @@
       </c>
       <c r="K407" s="3"/>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>460</v>
       </c>
@@ -17112,7 +17098,7 @@
       </c>
       <c r="K408" s="3"/>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>461</v>
       </c>
@@ -17142,7 +17128,7 @@
       </c>
       <c r="K409" s="3"/>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>462</v>
       </c>
@@ -17172,7 +17158,7 @@
       </c>
       <c r="K410" s="3"/>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>463</v>
       </c>
@@ -17202,7 +17188,7 @@
       </c>
       <c r="K411" s="3"/>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>464</v>
       </c>
@@ -17232,7 +17218,7 @@
       </c>
       <c r="K412" s="3"/>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>465</v>
       </c>
@@ -17250,7 +17236,7 @@
       <c r="J413" s="6"/>
       <c r="K413" s="3"/>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>466</v>
       </c>
@@ -17280,7 +17266,7 @@
       </c>
       <c r="K414" s="3"/>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>467</v>
       </c>
@@ -17298,7 +17284,7 @@
       <c r="J415" s="4"/>
       <c r="K415" s="3"/>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>468</v>
       </c>
@@ -17316,7 +17302,7 @@
       <c r="J416" s="4"/>
       <c r="K416" s="3"/>
     </row>
-    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>469</v>
       </c>
@@ -17334,7 +17320,7 @@
       <c r="J417" s="4"/>
       <c r="K417" s="3"/>
     </row>
-    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>470</v>
       </c>
@@ -17352,7 +17338,7 @@
       <c r="J418" s="4"/>
       <c r="K418" s="3"/>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>471</v>
       </c>
@@ -17382,7 +17368,7 @@
       </c>
       <c r="K419" s="3"/>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>472</v>
       </c>
@@ -17412,7 +17398,7 @@
       </c>
       <c r="K420" s="3"/>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>473</v>
       </c>
@@ -17442,7 +17428,7 @@
       </c>
       <c r="K421" s="3"/>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>474</v>
       </c>
@@ -17472,7 +17458,7 @@
       </c>
       <c r="K422" s="3"/>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>475</v>
       </c>
@@ -17502,7 +17488,7 @@
       </c>
       <c r="K423" s="3"/>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>476</v>
       </c>
@@ -17532,7 +17518,7 @@
       </c>
       <c r="K424" s="3"/>
     </row>
-    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>477</v>
       </c>
@@ -17550,7 +17536,7 @@
       <c r="J425" s="4"/>
       <c r="K425" s="3"/>
     </row>
-    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>478</v>
       </c>
@@ -17568,7 +17554,7 @@
       <c r="J426" s="4"/>
       <c r="K426" s="3"/>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>479</v>
       </c>
@@ -17598,7 +17584,7 @@
       </c>
       <c r="K427" s="3"/>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>480</v>
       </c>
@@ -17628,7 +17614,7 @@
       </c>
       <c r="K428" s="3"/>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>481</v>
       </c>
@@ -17658,7 +17644,7 @@
       </c>
       <c r="K429" s="3"/>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>482</v>
       </c>
@@ -17688,7 +17674,7 @@
       </c>
       <c r="K430" s="3"/>
     </row>
-    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>483</v>
       </c>
@@ -17706,7 +17692,7 @@
       <c r="J431" s="6"/>
       <c r="K431" s="3"/>
     </row>
-    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>484</v>
       </c>
@@ -17724,7 +17710,7 @@
       <c r="J432" s="4"/>
       <c r="K432" s="3"/>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>485</v>
       </c>
@@ -17742,7 +17728,7 @@
       <c r="J433" s="4"/>
       <c r="K433" s="3"/>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>486</v>
       </c>
@@ -17772,7 +17758,7 @@
       </c>
       <c r="K434" s="3"/>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>487</v>
       </c>
@@ -17815,14 +17801,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040BF47F-E9DD-47FE-8A77-28B9CE7118A4}">
   <dimension ref="B1:E421"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="80.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="80.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>33</v>
       </c>
@@ -17836,7 +17822,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>288</v>
       </c>
@@ -17848,7 +17834,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>282</v>
       </c>
@@ -17860,7 +17846,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>318</v>
       </c>
@@ -17872,7 +17858,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>288</v>
       </c>
@@ -17884,7 +17870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>231</v>
       </c>
@@ -17896,7 +17882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>288</v>
       </c>
@@ -17908,7 +17894,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>318</v>
       </c>
@@ -17920,7 +17906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>318</v>
       </c>
@@ -17932,7 +17918,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>318</v>
       </c>
@@ -17944,7 +17930,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>318</v>
       </c>
@@ -17956,7 +17942,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>318</v>
       </c>
@@ -17968,7 +17954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>318</v>
       </c>
@@ -17980,7 +17966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>318</v>
       </c>
@@ -17992,7 +17978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>180</v>
       </c>
@@ -18004,7 +17990,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>152</v>
       </c>
@@ -18016,7 +18002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>231</v>
       </c>
@@ -18028,7 +18014,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>115</v>
       </c>
@@ -18040,7 +18026,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>115</v>
       </c>
@@ -18052,7 +18038,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>282</v>
       </c>
@@ -18064,7 +18050,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>264</v>
       </c>
@@ -18076,7 +18062,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -18088,7 +18074,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>330</v>
       </c>
@@ -18100,7 +18086,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>335</v>
       </c>
@@ -18112,7 +18098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>71</v>
       </c>
@@ -18124,7 +18110,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>71</v>
       </c>
@@ -18136,7 +18122,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>61</v>
       </c>
@@ -18148,7 +18134,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>71</v>
       </c>
@@ -18160,7 +18146,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>71</v>
       </c>
@@ -18172,7 +18158,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>86</v>
       </c>
@@ -18184,7 +18170,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>86</v>
       </c>
@@ -18196,7 +18182,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>67</v>
       </c>
@@ -18208,7 +18194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>139</v>
       </c>
@@ -18220,7 +18206,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>166</v>
       </c>
@@ -18232,7 +18218,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>52</v>
       </c>
@@ -18244,7 +18230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>52</v>
       </c>
@@ -18256,7 +18242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>195</v>
       </c>
@@ -18268,7 +18254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>52</v>
       </c>
@@ -18280,7 +18266,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>238</v>
       </c>
@@ -18292,7 +18278,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>243</v>
       </c>
@@ -18304,7 +18290,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>360</v>
       </c>
@@ -18316,7 +18302,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>243</v>
       </c>
@@ -18328,7 +18314,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>180</v>
       </c>
@@ -18340,7 +18326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>152</v>
       </c>
@@ -18352,7 +18338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>335</v>
       </c>
@@ -18364,7 +18350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>166</v>
       </c>
@@ -18376,7 +18362,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>335</v>
       </c>
@@ -18388,7 +18374,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>166</v>
       </c>
@@ -18400,7 +18386,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>330</v>
       </c>
@@ -18412,7 +18398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>231</v>
       </c>
@@ -18424,7 +18410,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>152</v>
       </c>
@@ -18436,7 +18422,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>238</v>
       </c>
@@ -18448,7 +18434,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>335</v>
       </c>
@@ -18460,7 +18446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>152</v>
       </c>
@@ -18472,7 +18458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>152</v>
       </c>
@@ -18484,7 +18470,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>335</v>
       </c>
@@ -18496,7 +18482,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>335</v>
       </c>
@@ -18508,7 +18494,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>152</v>
       </c>
@@ -18520,7 +18506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>270</v>
       </c>
@@ -18532,7 +18518,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>308</v>
       </c>
@@ -18544,7 +18530,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>270</v>
       </c>
@@ -18556,7 +18542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>80</v>
       </c>
@@ -18568,7 +18554,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>308</v>
       </c>
@@ -18580,7 +18566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>270</v>
       </c>
@@ -18592,7 +18578,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>308</v>
       </c>
@@ -18604,7 +18590,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>308</v>
       </c>
@@ -18616,7 +18602,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>80</v>
       </c>
@@ -18628,7 +18614,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>355</v>
       </c>
@@ -18640,7 +18626,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>308</v>
       </c>
@@ -18652,7 +18638,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>355</v>
       </c>
@@ -18664,7 +18650,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>308</v>
       </c>
@@ -18676,7 +18662,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>355</v>
       </c>
@@ -18688,7 +18674,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>260</v>
       </c>
@@ -18700,7 +18686,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>260</v>
       </c>
@@ -18712,7 +18698,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>260</v>
       </c>
@@ -18724,7 +18710,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>260</v>
       </c>
@@ -18736,7 +18722,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>260</v>
       </c>
@@ -18748,7 +18734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>260</v>
       </c>
@@ -18760,7 +18746,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>260</v>
       </c>
@@ -18772,7 +18758,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>260</v>
       </c>
@@ -18784,7 +18770,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>260</v>
       </c>
@@ -18796,7 +18782,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>260</v>
       </c>
@@ -18808,7 +18794,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>260</v>
       </c>
@@ -18820,7 +18806,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>260</v>
       </c>
@@ -18832,7 +18818,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>260</v>
       </c>
@@ -18844,7 +18830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>218</v>
       </c>
@@ -18856,7 +18842,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>218</v>
       </c>
@@ -18868,7 +18854,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>218</v>
       </c>
@@ -18880,7 +18866,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>103</v>
       </c>
@@ -18892,7 +18878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>103</v>
       </c>
@@ -18904,7 +18890,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>103</v>
       </c>
@@ -18916,7 +18902,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>103</v>
       </c>
@@ -18928,7 +18914,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>103</v>
       </c>
@@ -18940,7 +18926,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>103</v>
       </c>
@@ -18952,7 +18938,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>103</v>
       </c>
@@ -18964,7 +18950,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>103</v>
       </c>
@@ -18976,7 +18962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>103</v>
       </c>
@@ -18988,7 +18974,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>243</v>
       </c>
@@ -19000,7 +18986,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>231</v>
       </c>
@@ -19012,7 +18998,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>330</v>
       </c>
@@ -19024,7 +19010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>238</v>
       </c>
@@ -19036,7 +19022,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>103</v>
       </c>
@@ -19048,7 +19034,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>103</v>
       </c>
@@ -19060,7 +19046,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>166</v>
       </c>
@@ -19072,7 +19058,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>335</v>
       </c>
@@ -19084,7 +19070,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>166</v>
       </c>
@@ -19096,7 +19082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>152</v>
       </c>
@@ -19108,7 +19094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>166</v>
       </c>
@@ -19120,7 +19106,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>166</v>
       </c>
@@ -19132,7 +19118,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>335</v>
       </c>
@@ -19144,7 +19130,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>218</v>
       </c>
@@ -19156,7 +19142,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>152</v>
       </c>
@@ -19168,7 +19154,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>218</v>
       </c>
@@ -19180,7 +19166,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>218</v>
       </c>
@@ -19192,7 +19178,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>335</v>
       </c>
@@ -19204,7 +19190,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>166</v>
       </c>
@@ -19216,7 +19202,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>166</v>
       </c>
@@ -19228,7 +19214,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>103</v>
       </c>
@@ -19240,7 +19226,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>103</v>
       </c>
@@ -19252,7 +19238,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>103</v>
       </c>
@@ -19264,7 +19250,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>103</v>
       </c>
@@ -19276,7 +19262,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>103</v>
       </c>
@@ -19288,7 +19274,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>103</v>
       </c>
@@ -19300,7 +19286,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>103</v>
       </c>
@@ -19312,7 +19298,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>133</v>
       </c>
@@ -19324,7 +19310,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>243</v>
       </c>
@@ -19336,7 +19322,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>243</v>
       </c>
@@ -19348,7 +19334,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>243</v>
       </c>
@@ -19360,7 +19346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>152</v>
       </c>
@@ -19372,7 +19358,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>335</v>
       </c>
@@ -19384,7 +19370,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>166</v>
       </c>
@@ -19396,7 +19382,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>335</v>
       </c>
@@ -19408,7 +19394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>335</v>
       </c>
@@ -19420,7 +19406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>335</v>
       </c>
@@ -19432,7 +19418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>260</v>
       </c>
@@ -19444,7 +19430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>260</v>
       </c>
@@ -19456,7 +19442,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>260</v>
       </c>
@@ -19468,7 +19454,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>218</v>
       </c>
@@ -19480,7 +19466,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>335</v>
       </c>
@@ -19492,7 +19478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>218</v>
       </c>
@@ -19504,7 +19490,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>335</v>
       </c>
@@ -19516,7 +19502,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>152</v>
       </c>
@@ -19528,7 +19514,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>152</v>
       </c>
@@ -19540,7 +19526,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>166</v>
       </c>
@@ -19552,7 +19538,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>152</v>
       </c>
@@ -19564,7 +19550,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>330</v>
       </c>
@@ -19576,7 +19562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>166</v>
       </c>
@@ -19588,7 +19574,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>166</v>
       </c>
@@ -19600,7 +19586,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>335</v>
       </c>
@@ -19612,7 +19598,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>238</v>
       </c>
@@ -19624,7 +19610,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>335</v>
       </c>
@@ -19636,7 +19622,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>218</v>
       </c>
@@ -19648,7 +19634,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>152</v>
       </c>
@@ -19660,7 +19646,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
         <v>335</v>
       </c>
@@ -19672,7 +19658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>270</v>
       </c>
@@ -19684,7 +19670,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>133</v>
       </c>
@@ -19696,7 +19682,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>133</v>
       </c>
@@ -19708,7 +19694,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>231</v>
       </c>
@@ -19720,7 +19706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>231</v>
       </c>
@@ -19732,7 +19718,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>288</v>
       </c>
@@ -19744,7 +19730,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>288</v>
       </c>
@@ -19756,7 +19742,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
         <v>288</v>
       </c>
@@ -19768,7 +19754,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>288</v>
       </c>
@@ -19780,7 +19766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
         <v>288</v>
       </c>
@@ -19792,7 +19778,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
         <v>288</v>
       </c>
@@ -19804,7 +19790,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>288</v>
       </c>
@@ -19816,7 +19802,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>115</v>
       </c>
@@ -19828,7 +19814,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>288</v>
       </c>
@@ -19840,7 +19826,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>103</v>
       </c>
@@ -19852,7 +19838,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
         <v>103</v>
       </c>
@@ -19864,7 +19850,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
         <v>103</v>
       </c>
@@ -19876,7 +19862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
         <v>103</v>
       </c>
@@ -19888,7 +19874,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
         <v>133</v>
       </c>
@@ -19900,7 +19886,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>133</v>
       </c>
@@ -19912,7 +19898,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
         <v>355</v>
       </c>
@@ -19924,7 +19910,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>249</v>
       </c>
@@ -19936,7 +19922,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>103</v>
       </c>
@@ -19948,7 +19934,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>103</v>
       </c>
@@ -19960,7 +19946,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>115</v>
       </c>
@@ -19972,7 +19958,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>115</v>
       </c>
@@ -19984,7 +19970,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>115</v>
       </c>
@@ -19996,7 +19982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>139</v>
       </c>
@@ -20008,7 +19994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>139</v>
       </c>
@@ -20020,7 +20006,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>139</v>
       </c>
@@ -20032,7 +20018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>139</v>
       </c>
@@ -20044,7 +20030,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>139</v>
       </c>
@@ -20056,7 +20042,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
         <v>139</v>
       </c>
@@ -20068,7 +20054,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>139</v>
       </c>
@@ -20080,7 +20066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>139</v>
       </c>
@@ -20092,7 +20078,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
         <v>139</v>
       </c>
@@ -20104,7 +20090,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
         <v>139</v>
       </c>
@@ -20116,7 +20102,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
         <v>139</v>
       </c>
@@ -20128,7 +20114,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
         <v>274</v>
       </c>
@@ -20140,7 +20126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
         <v>274</v>
       </c>
@@ -20152,7 +20138,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
         <v>274</v>
       </c>
@@ -20164,7 +20150,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
         <v>274</v>
       </c>
@@ -20176,7 +20162,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
         <v>86</v>
       </c>
@@ -20188,7 +20174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
         <v>86</v>
       </c>
@@ -20200,7 +20186,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
         <v>86</v>
       </c>
@@ -20212,7 +20198,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>86</v>
       </c>
@@ -20224,7 +20210,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
         <v>86</v>
       </c>
@@ -20236,7 +20222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>86</v>
       </c>
@@ -20248,7 +20234,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
         <v>86</v>
       </c>
@@ -20260,7 +20246,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
         <v>86</v>
       </c>
@@ -20272,7 +20258,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>86</v>
       </c>
@@ -20284,7 +20270,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>86</v>
       </c>
@@ -20296,7 +20282,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>86</v>
       </c>
@@ -20308,7 +20294,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
         <v>86</v>
       </c>
@@ -20320,7 +20306,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
         <v>86</v>
       </c>
@@ -20332,7 +20318,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
         <v>274</v>
       </c>
@@ -20344,7 +20330,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
         <v>274</v>
       </c>
@@ -20356,7 +20342,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
         <v>360</v>
       </c>
@@ -20368,7 +20354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
         <v>231</v>
       </c>
@@ -20380,7 +20366,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>231</v>
       </c>
@@ -20392,7 +20378,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
         <v>51</v>
       </c>
@@ -20407,7 +20393,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>86</v>
       </c>
@@ -20419,7 +20405,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
         <v>35</v>
       </c>
@@ -20431,7 +20417,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
         <v>35</v>
       </c>
@@ -20443,7 +20429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
         <v>35</v>
       </c>
@@ -20455,7 +20441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>35</v>
       </c>
@@ -20467,7 +20453,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>35</v>
       </c>
@@ -20479,7 +20465,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>35</v>
       </c>
@@ -20491,7 +20477,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
         <v>35</v>
       </c>
@@ -20503,7 +20489,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
         <v>35</v>
       </c>
@@ -20515,7 +20501,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>35</v>
       </c>
@@ -20527,7 +20513,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
         <v>35</v>
       </c>
@@ -20539,7 +20525,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>35</v>
       </c>
@@ -20551,7 +20537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
         <v>35</v>
       </c>
@@ -20563,7 +20549,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
         <v>35</v>
       </c>
@@ -20575,7 +20561,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
         <v>35</v>
       </c>
@@ -20587,7 +20573,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>35</v>
       </c>
@@ -20599,7 +20585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
         <v>35</v>
       </c>
@@ -20611,7 +20597,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>35</v>
       </c>
@@ -20623,7 +20609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
         <v>35</v>
       </c>
@@ -20635,7 +20621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
         <v>35</v>
       </c>
@@ -20647,7 +20633,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
         <v>35</v>
       </c>
@@ -20659,7 +20645,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>35</v>
       </c>
@@ -20671,7 +20657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
         <v>35</v>
       </c>
@@ -20683,7 +20669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>35</v>
       </c>
@@ -20695,7 +20681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>35</v>
       </c>
@@ -20707,7 +20693,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>35</v>
       </c>
@@ -20719,7 +20705,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>115</v>
       </c>
@@ -20731,7 +20717,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
         <v>80</v>
       </c>
@@ -20743,7 +20729,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
         <v>115</v>
       </c>
@@ -20755,7 +20741,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
         <v>318</v>
       </c>
@@ -20767,7 +20753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>180</v>
       </c>
@@ -20779,7 +20765,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>180</v>
       </c>
@@ -20791,7 +20777,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
         <v>180</v>
       </c>
@@ -20803,7 +20789,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
         <v>180</v>
       </c>
@@ -20815,7 +20801,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
         <v>180</v>
       </c>
@@ -20827,7 +20813,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>180</v>
       </c>
@@ -20839,7 +20825,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
         <v>318</v>
       </c>
@@ -20851,7 +20837,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
         <v>318</v>
       </c>
@@ -20863,7 +20849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
         <v>282</v>
       </c>
@@ -20875,7 +20861,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
         <v>218</v>
       </c>
@@ -20887,7 +20873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
         <v>67</v>
       </c>
@@ -20899,7 +20885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
         <v>61</v>
       </c>
@@ -20911,7 +20897,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
         <v>264</v>
       </c>
@@ -20923,7 +20909,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
         <v>264</v>
       </c>
@@ -20935,7 +20921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
         <v>264</v>
       </c>
@@ -20947,7 +20933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
         <v>264</v>
       </c>
@@ -20959,7 +20945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
         <v>218</v>
       </c>
@@ -20971,7 +20957,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
         <v>218</v>
       </c>
@@ -20983,7 +20969,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
         <v>260</v>
       </c>
@@ -20995,7 +20981,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
         <v>249</v>
       </c>
@@ -21007,7 +20993,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
         <v>260</v>
       </c>
@@ -21019,7 +21005,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
         <v>249</v>
       </c>
@@ -21031,7 +21017,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
         <v>249</v>
       </c>
@@ -21043,7 +21029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
         <v>249</v>
       </c>
@@ -21055,7 +21041,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
         <v>249</v>
       </c>
@@ -21067,7 +21053,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
         <v>260</v>
       </c>
@@ -21079,7 +21065,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
         <v>249</v>
       </c>
@@ -21091,7 +21077,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
         <v>360</v>
       </c>
@@ -21103,7 +21089,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
         <v>360</v>
       </c>
@@ -21115,7 +21101,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
         <v>360</v>
       </c>
@@ -21127,7 +21113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
         <v>360</v>
       </c>
@@ -21139,7 +21125,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
         <v>360</v>
       </c>
@@ -21151,7 +21137,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
         <v>360</v>
       </c>
@@ -21163,7 +21149,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
         <v>360</v>
       </c>
@@ -21175,7 +21161,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
         <v>360</v>
       </c>
@@ -21187,7 +21173,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
         <v>360</v>
       </c>
@@ -21199,7 +21185,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
         <v>360</v>
       </c>
@@ -21211,7 +21197,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
         <v>282</v>
       </c>
@@ -21223,7 +21209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
         <v>51</v>
       </c>
@@ -21238,7 +21224,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
         <v>51</v>
       </c>
@@ -21253,7 +21239,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
         <v>51</v>
       </c>
@@ -21268,7 +21254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
         <v>35</v>
       </c>
@@ -21280,7 +21266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
         <v>35</v>
       </c>
@@ -21292,7 +21278,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
         <v>35</v>
       </c>
@@ -21304,7 +21290,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
         <v>35</v>
       </c>
@@ -21316,7 +21302,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
         <v>71</v>
       </c>
@@ -21328,7 +21314,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
         <v>249</v>
       </c>
@@ -21340,7 +21326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
         <v>71</v>
       </c>
@@ -21352,7 +21338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
         <v>71</v>
       </c>
@@ -21364,7 +21350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
         <v>71</v>
       </c>
@@ -21376,7 +21362,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
         <v>282</v>
       </c>
@@ -21388,7 +21374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
         <v>218</v>
       </c>
@@ -21400,7 +21386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
         <v>61</v>
       </c>
@@ -21412,7 +21398,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
         <v>218</v>
       </c>
@@ -21424,7 +21410,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
         <v>218</v>
       </c>
@@ -21436,7 +21422,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
         <v>218</v>
       </c>
@@ -21448,7 +21434,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
         <v>218</v>
       </c>
@@ -21460,7 +21446,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
         <v>218</v>
       </c>
@@ -21472,7 +21458,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
         <v>218</v>
       </c>
@@ -21484,7 +21470,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
         <v>260</v>
       </c>
@@ -21496,7 +21482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
         <v>71</v>
       </c>
@@ -21508,7 +21494,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
         <v>282</v>
       </c>
@@ -21520,7 +21506,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
         <v>308</v>
       </c>
@@ -21532,7 +21518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
         <v>308</v>
       </c>
@@ -21544,7 +21530,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
         <v>67</v>
       </c>
@@ -21556,7 +21542,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
         <v>61</v>
       </c>
@@ -21568,7 +21554,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
         <v>61</v>
       </c>
@@ -21580,7 +21566,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
         <v>218</v>
       </c>
@@ -21592,7 +21578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
         <v>71</v>
       </c>
@@ -21604,7 +21590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
         <v>249</v>
       </c>
@@ -21616,7 +21602,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
         <v>71</v>
       </c>
@@ -21628,7 +21614,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
         <v>71</v>
       </c>
@@ -21640,7 +21626,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
         <v>71</v>
       </c>
@@ -21652,7 +21638,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
         <v>71</v>
       </c>
@@ -21664,7 +21650,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
         <v>195</v>
       </c>
@@ -21676,7 +21662,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
         <v>195</v>
       </c>
@@ -21688,7 +21674,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
         <v>195</v>
       </c>
@@ -21700,7 +21686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" t="s">
         <v>195</v>
       </c>
@@ -21712,7 +21698,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" t="s">
         <v>195</v>
       </c>
@@ -21724,7 +21710,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>195</v>
       </c>
@@ -21736,7 +21722,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" t="s">
         <v>195</v>
       </c>
@@ -21748,7 +21734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" t="s">
         <v>195</v>
       </c>
@@ -21760,7 +21746,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
         <v>195</v>
       </c>
@@ -21772,7 +21758,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
         <v>195</v>
       </c>
@@ -21784,7 +21770,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" t="s">
         <v>195</v>
       </c>
@@ -21796,7 +21782,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
         <v>195</v>
       </c>
@@ -21808,7 +21794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
         <v>195</v>
       </c>
@@ -21820,7 +21806,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" t="s">
         <v>195</v>
       </c>
@@ -21832,7 +21818,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
         <v>195</v>
       </c>
@@ -21844,7 +21830,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" t="s">
         <v>195</v>
       </c>
@@ -21856,7 +21842,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>195</v>
       </c>
@@ -21868,7 +21854,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
         <v>195</v>
       </c>
@@ -21880,7 +21866,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>195</v>
       </c>
@@ -21892,7 +21878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>195</v>
       </c>
@@ -21904,7 +21890,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
         <v>218</v>
       </c>
@@ -21916,7 +21902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
         <v>218</v>
       </c>
@@ -21928,7 +21914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
         <v>308</v>
       </c>
@@ -21940,7 +21926,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B343" t="s">
         <v>318</v>
       </c>
@@ -21952,7 +21938,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B344" t="s">
         <v>318</v>
       </c>
@@ -21964,7 +21950,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B345" t="s">
         <v>318</v>
       </c>
@@ -21976,7 +21962,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
         <v>318</v>
       </c>
@@ -21988,7 +21974,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B347" t="s">
         <v>318</v>
       </c>
@@ -22000,7 +21986,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B348" t="s">
         <v>360</v>
       </c>
@@ -22012,7 +21998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B349" t="s">
         <v>360</v>
       </c>
@@ -22024,7 +22010,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B350" t="s">
         <v>308</v>
       </c>
@@ -22036,7 +22022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B351" t="s">
         <v>318</v>
       </c>
@@ -22048,7 +22034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B352" t="s">
         <v>115</v>
       </c>
@@ -22060,7 +22046,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B353" t="s">
         <v>115</v>
       </c>
@@ -22072,7 +22058,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>115</v>
       </c>
@@ -22084,7 +22070,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B355" t="s">
         <v>115</v>
       </c>
@@ -22096,7 +22082,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>152</v>
       </c>
@@ -22108,7 +22094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B357" t="s">
         <v>152</v>
       </c>
@@ -22120,7 +22106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B358" t="s">
         <v>152</v>
       </c>
@@ -22132,7 +22118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B359" t="s">
         <v>152</v>
       </c>
@@ -22144,7 +22130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B360" t="s">
         <v>152</v>
       </c>
@@ -22156,7 +22142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B361" t="s">
         <v>52</v>
       </c>
@@ -22168,7 +22154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B362" t="s">
         <v>52</v>
       </c>
@@ -22180,7 +22166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B363" t="s">
         <v>52</v>
       </c>
@@ -22192,7 +22178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B364" t="s">
         <v>152</v>
       </c>
@@ -22204,7 +22190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B365" t="s">
         <v>152</v>
       </c>
@@ -22216,7 +22202,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B366" t="s">
         <v>52</v>
       </c>
@@ -22228,7 +22214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B367" t="s">
         <v>152</v>
       </c>
@@ -22240,7 +22226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B368" t="s">
         <v>152</v>
       </c>
@@ -22252,7 +22238,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B369" t="s">
         <v>152</v>
       </c>
@@ -22264,7 +22250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B370" t="s">
         <v>52</v>
       </c>
@@ -22276,7 +22262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B371" t="s">
         <v>152</v>
       </c>
@@ -22288,7 +22274,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>152</v>
       </c>
@@ -22300,7 +22286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B373" t="s">
         <v>52</v>
       </c>
@@ -22312,7 +22298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B374" t="s">
         <v>52</v>
       </c>
@@ -22324,7 +22310,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B375" t="s">
         <v>52</v>
       </c>
@@ -22336,7 +22322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B376" t="s">
         <v>288</v>
       </c>
@@ -22348,7 +22334,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B377" t="s">
         <v>180</v>
       </c>
@@ -22360,7 +22346,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B378" t="s">
         <v>180</v>
       </c>
@@ -22372,7 +22358,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B379" t="s">
         <v>180</v>
       </c>
@@ -22384,7 +22370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B380" t="s">
         <v>180</v>
       </c>
@@ -22396,7 +22382,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B381" t="s">
         <v>274</v>
       </c>
@@ -22408,7 +22394,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>318</v>
       </c>
@@ -22420,7 +22406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B383" t="s">
         <v>318</v>
       </c>
@@ -22432,7 +22418,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B384" t="s">
         <v>318</v>
       </c>
@@ -22444,7 +22430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B385" t="s">
         <v>318</v>
       </c>
@@ -22456,7 +22442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B386" t="s">
         <v>318</v>
       </c>
@@ -22468,7 +22454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B387" t="s">
         <v>308</v>
       </c>
@@ -22480,7 +22466,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B388" t="s">
         <v>249</v>
       </c>
@@ -22492,7 +22478,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B389" t="s">
         <v>195</v>
       </c>
@@ -22504,7 +22490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B390" t="s">
         <v>274</v>
       </c>
@@ -22516,7 +22502,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B391" t="s">
         <v>282</v>
       </c>
@@ -22528,7 +22514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B392" t="s">
         <v>282</v>
       </c>
@@ -22540,7 +22526,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B393" t="s">
         <v>288</v>
       </c>
@@ -22552,7 +22538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B394" t="s">
         <v>288</v>
       </c>
@@ -22564,7 +22550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B395" t="s">
         <v>288</v>
       </c>
@@ -22576,7 +22562,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B396" t="s">
         <v>288</v>
       </c>
@@ -22588,7 +22574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B397" t="s">
         <v>115</v>
       </c>
@@ -22600,7 +22586,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B398" t="s">
         <v>80</v>
       </c>
@@ -22612,7 +22598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B399" t="s">
         <v>288</v>
       </c>
@@ -22624,7 +22610,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B400" t="s">
         <v>318</v>
       </c>
@@ -22636,7 +22622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B401" t="s">
         <v>335</v>
       </c>
@@ -22648,7 +22634,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B402" t="s">
         <v>288</v>
       </c>
@@ -22660,7 +22646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B403" t="s">
         <v>288</v>
       </c>
@@ -22672,7 +22658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B404" t="s">
         <v>288</v>
       </c>
@@ -22684,7 +22670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B405" t="s">
         <v>318</v>
       </c>
@@ -22696,7 +22682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B406" t="s">
         <v>115</v>
       </c>
@@ -22708,7 +22694,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B407" t="s">
         <v>288</v>
       </c>
@@ -22720,7 +22706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B408" t="s">
         <v>180</v>
       </c>
@@ -22732,7 +22718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B409" t="s">
         <v>80</v>
       </c>
@@ -22744,7 +22730,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B410" t="s">
         <v>115</v>
       </c>
@@ -22756,7 +22742,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B411" t="s">
         <v>115</v>
       </c>
@@ -22768,7 +22754,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B412" t="s">
         <v>115</v>
       </c>
@@ -22780,7 +22766,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B413" t="s">
         <v>180</v>
       </c>
@@ -22792,7 +22778,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B414" t="s">
         <v>282</v>
       </c>
@@ -22804,7 +22790,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B415" t="s">
         <v>318</v>
       </c>
@@ -22816,7 +22802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B416" t="s">
         <v>288</v>
       </c>
@@ -22828,7 +22814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B417" t="s">
         <v>34</v>
       </c>
@@ -22840,7 +22826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B418" t="s">
         <v>67</v>
       </c>
@@ -22852,7 +22838,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B419" t="s">
         <v>218</v>
       </c>
@@ -22864,7 +22850,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B420" t="s">
         <v>318</v>
       </c>
@@ -22876,7 +22862,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B421" t="s">
         <v>34</v>
       </c>
